--- a/DBs/wnba/Results/WNBA_2024_Results.xlsx
+++ b/DBs/wnba/Results/WNBA_2024_Results.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tjsut\TracerSports\WNBA_Elo\Results\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tjsut\tracersports-app\DBs\wnba\Results\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FB80E8FC-EF55-40EA-A66D-5A1D2E8AC381}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BD2CECE2-B35B-4BED-9E52-AAB41F95F2E5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{1654EDFA-4626-4D72-A032-E72CC9A130FE}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2586" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2594" uniqueCount="27">
   <si>
     <t>Date</t>
   </si>
@@ -179,8 +179,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{6761A9D6-0284-4780-BB0F-50A0FFF04726}" name="Table1" displayName="Table1" ref="A1:J525" totalsRowShown="0">
-  <autoFilter ref="A1:J525" xr:uid="{6761A9D6-0284-4780-BB0F-50A0FFF04726}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{6761A9D6-0284-4780-BB0F-50A0FFF04726}" name="Table1" displayName="Table1" ref="A1:J527" totalsRowShown="0">
+  <autoFilter ref="A1:J527" xr:uid="{6761A9D6-0284-4780-BB0F-50A0FFF04726}"/>
   <tableColumns count="10">
     <tableColumn id="1" xr3:uid="{9606CA38-2371-480A-B2F8-3A23285B655E}" name="Date" dataDxfId="0"/>
     <tableColumn id="2" xr3:uid="{B29C85CC-3DBC-401B-A183-ABA3F92B96B9}" name="Season"/>
@@ -514,7 +514,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A4FB24B2-7646-4F57-8F9C-DF3DFCDB2AF4}">
-  <dimension ref="A1:J525"/>
+  <dimension ref="A1:J527"/>
   <sheetFormatPr defaultRowHeight="15.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="9.9140625" bestFit="1" customWidth="1"/>
@@ -6770,31 +6770,31 @@
     </row>
     <row r="196" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A196" s="1">
-        <v>45470</v>
+        <v>45468</v>
       </c>
       <c r="B196">
         <v>2024</v>
       </c>
       <c r="C196" t="s">
-        <v>10</v>
-      </c>
-      <c r="D196" t="s">
-        <v>11</v>
+        <v>23</v>
+      </c>
+      <c r="D196">
+        <v>0.1</v>
       </c>
       <c r="E196" t="s">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="F196" t="s">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="G196" t="s">
         <v>25</v>
       </c>
       <c r="H196">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="I196">
-        <v>83</v>
+        <v>89</v>
       </c>
       <c r="J196">
         <v>0</v>
@@ -6802,31 +6802,31 @@
     </row>
     <row r="197" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A197" s="1">
-        <v>45470</v>
+        <v>45468</v>
       </c>
       <c r="B197">
         <v>2024</v>
       </c>
       <c r="C197" t="s">
-        <v>10</v>
-      </c>
-      <c r="D197" t="s">
-        <v>11</v>
+        <v>23</v>
+      </c>
+      <c r="D197">
+        <v>0.1</v>
       </c>
       <c r="E197" t="s">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="F197" t="s">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="G197" t="s">
         <v>26</v>
       </c>
       <c r="H197">
-        <v>83</v>
+        <v>89</v>
       </c>
       <c r="I197">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="J197">
         <v>0</v>
@@ -6846,19 +6846,19 @@
         <v>11</v>
       </c>
       <c r="E198" t="s">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="F198" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="G198" t="s">
         <v>25</v>
       </c>
       <c r="H198">
-        <v>88</v>
+        <v>95</v>
       </c>
       <c r="I198">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="J198">
         <v>0</v>
@@ -6878,19 +6878,19 @@
         <v>11</v>
       </c>
       <c r="E199" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="F199" t="s">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="G199" t="s">
         <v>26</v>
       </c>
       <c r="H199">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="I199">
-        <v>88</v>
+        <v>95</v>
       </c>
       <c r="J199">
         <v>0</v>
@@ -6910,19 +6910,19 @@
         <v>11</v>
       </c>
       <c r="E200" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="F200" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="G200" t="s">
         <v>25</v>
       </c>
       <c r="H200">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="I200">
-        <v>89</v>
+        <v>94</v>
       </c>
       <c r="J200">
         <v>0</v>
@@ -6942,19 +6942,19 @@
         <v>11</v>
       </c>
       <c r="E201" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="F201" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="G201" t="s">
         <v>26</v>
       </c>
       <c r="H201">
-        <v>89</v>
+        <v>94</v>
       </c>
       <c r="I201">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="J201">
         <v>0</v>
@@ -6974,22 +6974,22 @@
         <v>11</v>
       </c>
       <c r="E202" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="F202" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="G202" t="s">
         <v>25</v>
       </c>
       <c r="H202">
-        <v>94</v>
+        <v>77</v>
       </c>
       <c r="I202">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="J202">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="203" spans="1:10" x14ac:dyDescent="0.35">
@@ -7006,27 +7006,27 @@
         <v>11</v>
       </c>
       <c r="E203" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="F203" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="G203" t="s">
         <v>26</v>
       </c>
       <c r="H203">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="I203">
-        <v>94</v>
+        <v>77</v>
       </c>
       <c r="J203">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="204" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A204" s="1">
-        <v>45471</v>
+        <v>45470</v>
       </c>
       <c r="B204">
         <v>2024</v>
@@ -7038,27 +7038,27 @@
         <v>11</v>
       </c>
       <c r="E204" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="F204" t="s">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="G204" t="s">
         <v>25</v>
       </c>
       <c r="H204">
-        <v>78</v>
+        <v>94</v>
       </c>
       <c r="I204">
-        <v>74</v>
+        <v>91</v>
       </c>
       <c r="J204">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="205" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A205" s="1">
-        <v>45471</v>
+        <v>45470</v>
       </c>
       <c r="B205">
         <v>2024</v>
@@ -7070,22 +7070,22 @@
         <v>11</v>
       </c>
       <c r="E205" t="s">
+        <v>12</v>
+      </c>
+      <c r="F205" t="s">
         <v>19</v>
       </c>
-      <c r="F205" t="s">
-        <v>21</v>
-      </c>
       <c r="G205" t="s">
         <v>26</v>
       </c>
       <c r="H205">
-        <v>74</v>
+        <v>91</v>
       </c>
       <c r="I205">
-        <v>78</v>
+        <v>94</v>
       </c>
       <c r="J205">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="206" spans="1:10" x14ac:dyDescent="0.35">
@@ -7102,10 +7102,10 @@
         <v>11</v>
       </c>
       <c r="E206" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="F206" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="G206" t="s">
         <v>25</v>
@@ -7114,7 +7114,7 @@
         <v>78</v>
       </c>
       <c r="I206">
-        <v>92</v>
+        <v>74</v>
       </c>
       <c r="J206">
         <v>0</v>
@@ -7134,16 +7134,16 @@
         <v>11</v>
       </c>
       <c r="E207" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="F207" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="G207" t="s">
         <v>26</v>
       </c>
       <c r="H207">
-        <v>92</v>
+        <v>74</v>
       </c>
       <c r="I207">
         <v>78</v>
@@ -7154,7 +7154,7 @@
     </row>
     <row r="208" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A208" s="1">
-        <v>45472</v>
+        <v>45471</v>
       </c>
       <c r="B208">
         <v>2024</v>
@@ -7166,19 +7166,19 @@
         <v>11</v>
       </c>
       <c r="E208" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="F208" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="G208" t="s">
         <v>25</v>
       </c>
       <c r="H208">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="I208">
-        <v>97</v>
+        <v>92</v>
       </c>
       <c r="J208">
         <v>0</v>
@@ -7186,7 +7186,7 @@
     </row>
     <row r="209" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A209" s="1">
-        <v>45472</v>
+        <v>45471</v>
       </c>
       <c r="B209">
         <v>2024</v>
@@ -7198,19 +7198,19 @@
         <v>11</v>
       </c>
       <c r="E209" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="F209" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="G209" t="s">
         <v>26</v>
       </c>
       <c r="H209">
-        <v>97</v>
+        <v>92</v>
       </c>
       <c r="I209">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="J209">
         <v>0</v>
@@ -7230,19 +7230,19 @@
         <v>11</v>
       </c>
       <c r="E210" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="F210" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="G210" t="s">
         <v>25</v>
       </c>
       <c r="H210">
-        <v>88</v>
+        <v>76</v>
       </c>
       <c r="I210">
-        <v>77</v>
+        <v>97</v>
       </c>
       <c r="J210">
         <v>0</v>
@@ -7262,19 +7262,19 @@
         <v>11</v>
       </c>
       <c r="E211" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="F211" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="G211" t="s">
         <v>26</v>
       </c>
       <c r="H211">
-        <v>77</v>
+        <v>97</v>
       </c>
       <c r="I211">
-        <v>88</v>
+        <v>76</v>
       </c>
       <c r="J211">
         <v>0</v>
@@ -7282,7 +7282,7 @@
     </row>
     <row r="212" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A212" s="1">
-        <v>45473</v>
+        <v>45472</v>
       </c>
       <c r="B212">
         <v>2024</v>
@@ -7294,19 +7294,19 @@
         <v>11</v>
       </c>
       <c r="E212" t="s">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="F212" t="s">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="G212" t="s">
         <v>25</v>
       </c>
       <c r="H212">
-        <v>70</v>
+        <v>88</v>
       </c>
       <c r="I212">
-        <v>62</v>
+        <v>77</v>
       </c>
       <c r="J212">
         <v>0</v>
@@ -7314,7 +7314,7 @@
     </row>
     <row r="213" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A213" s="1">
-        <v>45473</v>
+        <v>45472</v>
       </c>
       <c r="B213">
         <v>2024</v>
@@ -7326,19 +7326,19 @@
         <v>11</v>
       </c>
       <c r="E213" t="s">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="F213" t="s">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="G213" t="s">
         <v>26</v>
       </c>
       <c r="H213">
-        <v>62</v>
+        <v>77</v>
       </c>
       <c r="I213">
-        <v>70</v>
+        <v>88</v>
       </c>
       <c r="J213">
         <v>0</v>
@@ -7358,19 +7358,19 @@
         <v>11</v>
       </c>
       <c r="E214" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="F214" t="s">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="G214" t="s">
         <v>25</v>
       </c>
       <c r="H214">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="I214">
-        <v>81</v>
+        <v>62</v>
       </c>
       <c r="J214">
         <v>0</v>
@@ -7390,19 +7390,19 @@
         <v>11</v>
       </c>
       <c r="E215" t="s">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="F215" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="G215" t="s">
         <v>26</v>
       </c>
       <c r="H215">
-        <v>81</v>
+        <v>62</v>
       </c>
       <c r="I215">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="J215">
         <v>0</v>
@@ -7422,19 +7422,19 @@
         <v>11</v>
       </c>
       <c r="E216" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="F216" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G216" t="s">
         <v>25</v>
       </c>
       <c r="H216">
-        <v>88</v>
+        <v>75</v>
       </c>
       <c r="I216">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="J216">
         <v>0</v>
@@ -7454,19 +7454,19 @@
         <v>11</v>
       </c>
       <c r="E217" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F217" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="G217" t="s">
         <v>26</v>
       </c>
       <c r="H217">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="I217">
-        <v>88</v>
+        <v>75</v>
       </c>
       <c r="J217">
         <v>0</v>
@@ -7474,7 +7474,7 @@
     </row>
     <row r="218" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A218" s="1">
-        <v>45474</v>
+        <v>45473</v>
       </c>
       <c r="B218">
         <v>2024</v>
@@ -7486,7 +7486,7 @@
         <v>11</v>
       </c>
       <c r="E218" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="F218" t="s">
         <v>14</v>
@@ -7495,10 +7495,10 @@
         <v>25</v>
       </c>
       <c r="H218">
-        <v>83</v>
+        <v>88</v>
       </c>
       <c r="I218">
-        <v>72</v>
+        <v>82</v>
       </c>
       <c r="J218">
         <v>0</v>
@@ -7506,7 +7506,7 @@
     </row>
     <row r="219" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A219" s="1">
-        <v>45474</v>
+        <v>45473</v>
       </c>
       <c r="B219">
         <v>2024</v>
@@ -7521,16 +7521,16 @@
         <v>14</v>
       </c>
       <c r="F219" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="G219" t="s">
         <v>26</v>
       </c>
       <c r="H219">
-        <v>72</v>
+        <v>82</v>
       </c>
       <c r="I219">
-        <v>83</v>
+        <v>88</v>
       </c>
       <c r="J219">
         <v>0</v>
@@ -7550,19 +7550,19 @@
         <v>11</v>
       </c>
       <c r="E220" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="F220" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="G220" t="s">
         <v>25</v>
       </c>
       <c r="H220">
-        <v>71</v>
+        <v>83</v>
       </c>
       <c r="I220">
-        <v>95</v>
+        <v>72</v>
       </c>
       <c r="J220">
         <v>0</v>
@@ -7582,19 +7582,19 @@
         <v>11</v>
       </c>
       <c r="E221" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="F221" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="G221" t="s">
         <v>26</v>
       </c>
       <c r="H221">
-        <v>95</v>
+        <v>72</v>
       </c>
       <c r="I221">
-        <v>71</v>
+        <v>83</v>
       </c>
       <c r="J221">
         <v>0</v>
@@ -7602,7 +7602,7 @@
     </row>
     <row r="222" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A222" s="1">
-        <v>45475</v>
+        <v>45474</v>
       </c>
       <c r="B222">
         <v>2024</v>
@@ -7614,19 +7614,19 @@
         <v>11</v>
       </c>
       <c r="E222" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="F222" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="G222" t="s">
         <v>25</v>
       </c>
       <c r="H222">
-        <v>85</v>
+        <v>71</v>
       </c>
       <c r="I222">
-        <v>77</v>
+        <v>95</v>
       </c>
       <c r="J222">
         <v>0</v>
@@ -7634,7 +7634,7 @@
     </row>
     <row r="223" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A223" s="1">
-        <v>45475</v>
+        <v>45474</v>
       </c>
       <c r="B223">
         <v>2024</v>
@@ -7646,19 +7646,19 @@
         <v>11</v>
       </c>
       <c r="E223" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="F223" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="G223" t="s">
         <v>26</v>
       </c>
       <c r="H223">
-        <v>77</v>
+        <v>95</v>
       </c>
       <c r="I223">
-        <v>85</v>
+        <v>71</v>
       </c>
       <c r="J223">
         <v>0</v>
@@ -7678,19 +7678,19 @@
         <v>11</v>
       </c>
       <c r="E224" t="s">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="F224" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="G224" t="s">
         <v>25</v>
       </c>
       <c r="H224">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="I224">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="J224">
         <v>0</v>
@@ -7710,19 +7710,19 @@
         <v>11</v>
       </c>
       <c r="E225" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="F225" t="s">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="G225" t="s">
         <v>26</v>
       </c>
       <c r="H225">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="I225">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="J225">
         <v>0</v>
@@ -7742,19 +7742,19 @@
         <v>11</v>
       </c>
       <c r="E226" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="F226" t="s">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="G226" t="s">
         <v>25</v>
       </c>
       <c r="H226">
-        <v>69</v>
+        <v>82</v>
       </c>
       <c r="I226">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="J226">
         <v>0</v>
@@ -7774,19 +7774,19 @@
         <v>11</v>
       </c>
       <c r="E227" t="s">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="F227" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="G227" t="s">
         <v>26</v>
       </c>
       <c r="H227">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="I227">
-        <v>69</v>
+        <v>82</v>
       </c>
       <c r="J227">
         <v>0</v>
@@ -7806,19 +7806,19 @@
         <v>11</v>
       </c>
       <c r="E228" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="F228" t="s">
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="G228" t="s">
         <v>25</v>
       </c>
       <c r="H228">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="I228">
-        <v>76</v>
+        <v>88</v>
       </c>
       <c r="J228">
         <v>0</v>
@@ -7838,19 +7838,19 @@
         <v>11</v>
       </c>
       <c r="E229" t="s">
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="F229" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="G229" t="s">
         <v>26</v>
       </c>
       <c r="H229">
-        <v>76</v>
+        <v>88</v>
       </c>
       <c r="I229">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="J229">
         <v>0</v>
@@ -7858,7 +7858,7 @@
     </row>
     <row r="230" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A230" s="1">
-        <v>45476</v>
+        <v>45475</v>
       </c>
       <c r="B230">
         <v>2024</v>
@@ -7870,19 +7870,19 @@
         <v>11</v>
       </c>
       <c r="E230" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="F230" t="s">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="G230" t="s">
         <v>25</v>
       </c>
       <c r="H230">
-        <v>104</v>
+        <v>67</v>
       </c>
       <c r="I230">
-        <v>96</v>
+        <v>76</v>
       </c>
       <c r="J230">
         <v>0</v>
@@ -7890,7 +7890,7 @@
     </row>
     <row r="231" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A231" s="1">
-        <v>45476</v>
+        <v>45475</v>
       </c>
       <c r="B231">
         <v>2024</v>
@@ -7902,19 +7902,19 @@
         <v>11</v>
       </c>
       <c r="E231" t="s">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="F231" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="G231" t="s">
         <v>26</v>
       </c>
       <c r="H231">
-        <v>96</v>
+        <v>76</v>
       </c>
       <c r="I231">
-        <v>104</v>
+        <v>67</v>
       </c>
       <c r="J231">
         <v>0</v>
@@ -7922,7 +7922,7 @@
     </row>
     <row r="232" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A232" s="1">
-        <v>45477</v>
+        <v>45476</v>
       </c>
       <c r="B232">
         <v>2024</v>
@@ -7934,19 +7934,19 @@
         <v>11</v>
       </c>
       <c r="E232" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="F232" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="G232" t="s">
         <v>25</v>
       </c>
       <c r="H232">
-        <v>77</v>
+        <v>104</v>
       </c>
       <c r="I232">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="J232">
         <v>0</v>
@@ -7954,7 +7954,7 @@
     </row>
     <row r="233" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A233" s="1">
-        <v>45477</v>
+        <v>45476</v>
       </c>
       <c r="B233">
         <v>2024</v>
@@ -7966,19 +7966,19 @@
         <v>11</v>
       </c>
       <c r="E233" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="F233" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="G233" t="s">
         <v>26</v>
       </c>
       <c r="H233">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="I233">
-        <v>77</v>
+        <v>104</v>
       </c>
       <c r="J233">
         <v>0</v>
@@ -7998,19 +7998,19 @@
         <v>11</v>
       </c>
       <c r="E234" t="s">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="F234" t="s">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="G234" t="s">
         <v>25</v>
       </c>
       <c r="H234">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="I234">
-        <v>73</v>
+        <v>98</v>
       </c>
       <c r="J234">
         <v>0</v>
@@ -8030,19 +8030,19 @@
         <v>11</v>
       </c>
       <c r="E235" t="s">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="F235" t="s">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="G235" t="s">
         <v>26</v>
       </c>
       <c r="H235">
-        <v>73</v>
+        <v>98</v>
       </c>
       <c r="I235">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="J235">
         <v>0</v>
@@ -8050,7 +8050,7 @@
     </row>
     <row r="236" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A236" s="1">
-        <v>45478</v>
+        <v>45477</v>
       </c>
       <c r="B236">
         <v>2024</v>
@@ -8062,19 +8062,19 @@
         <v>11</v>
       </c>
       <c r="E236" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="F236" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="G236" t="s">
         <v>25</v>
       </c>
       <c r="H236">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="I236">
-        <v>85</v>
+        <v>73</v>
       </c>
       <c r="J236">
         <v>0</v>
@@ -8082,7 +8082,7 @@
     </row>
     <row r="237" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A237" s="1">
-        <v>45478</v>
+        <v>45477</v>
       </c>
       <c r="B237">
         <v>2024</v>
@@ -8094,19 +8094,19 @@
         <v>11</v>
       </c>
       <c r="E237" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="F237" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="G237" t="s">
         <v>26</v>
       </c>
       <c r="H237">
-        <v>85</v>
+        <v>73</v>
       </c>
       <c r="I237">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="J237">
         <v>0</v>
@@ -8126,22 +8126,22 @@
         <v>11</v>
       </c>
       <c r="E238" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="F238" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="G238" t="s">
         <v>25</v>
       </c>
       <c r="H238">
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="I238">
-        <v>98</v>
+        <v>85</v>
       </c>
       <c r="J238">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="239" spans="1:10" x14ac:dyDescent="0.35">
@@ -8158,22 +8158,22 @@
         <v>11</v>
       </c>
       <c r="E239" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="F239" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="G239" t="s">
         <v>26</v>
       </c>
       <c r="H239">
-        <v>98</v>
+        <v>85</v>
       </c>
       <c r="I239">
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="J239">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="240" spans="1:10" x14ac:dyDescent="0.35">
@@ -8190,22 +8190,22 @@
         <v>11</v>
       </c>
       <c r="E240" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="F240" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="G240" t="s">
         <v>25</v>
       </c>
       <c r="H240">
-        <v>88</v>
+        <v>93</v>
       </c>
       <c r="I240">
-        <v>84</v>
+        <v>98</v>
       </c>
       <c r="J240">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="241" spans="1:10" x14ac:dyDescent="0.35">
@@ -8222,27 +8222,27 @@
         <v>11</v>
       </c>
       <c r="E241" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F241" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="G241" t="s">
         <v>26</v>
       </c>
       <c r="H241">
-        <v>84</v>
+        <v>98</v>
       </c>
       <c r="I241">
-        <v>88</v>
+        <v>93</v>
       </c>
       <c r="J241">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="242" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A242" s="1">
-        <v>45479</v>
+        <v>45478</v>
       </c>
       <c r="B242">
         <v>2024</v>
@@ -8254,19 +8254,19 @@
         <v>11</v>
       </c>
       <c r="E242" t="s">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="F242" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="G242" t="s">
         <v>25</v>
       </c>
       <c r="H242">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="I242">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="J242">
         <v>0</v>
@@ -8274,7 +8274,7 @@
     </row>
     <row r="243" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A243" s="1">
-        <v>45479</v>
+        <v>45478</v>
       </c>
       <c r="B243">
         <v>2024</v>
@@ -8286,19 +8286,19 @@
         <v>11</v>
       </c>
       <c r="E243" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F243" t="s">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="G243" t="s">
         <v>26</v>
       </c>
       <c r="H243">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="I243">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="J243">
         <v>0</v>
@@ -8318,19 +8318,19 @@
         <v>11</v>
       </c>
       <c r="E244" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F244" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="G244" t="s">
         <v>25</v>
       </c>
       <c r="H244">
-        <v>67</v>
+        <v>78</v>
       </c>
       <c r="I244">
-        <v>74</v>
+        <v>83</v>
       </c>
       <c r="J244">
         <v>0</v>
@@ -8350,19 +8350,19 @@
         <v>11</v>
       </c>
       <c r="E245" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="F245" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G245" t="s">
         <v>26</v>
       </c>
       <c r="H245">
-        <v>74</v>
+        <v>83</v>
       </c>
       <c r="I245">
-        <v>67</v>
+        <v>78</v>
       </c>
       <c r="J245">
         <v>0</v>
@@ -8370,7 +8370,7 @@
     </row>
     <row r="246" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A246" s="1">
-        <v>45480</v>
+        <v>45479</v>
       </c>
       <c r="B246">
         <v>2024</v>
@@ -8382,10 +8382,10 @@
         <v>11</v>
       </c>
       <c r="E246" t="s">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="F246" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="G246" t="s">
         <v>25</v>
@@ -8394,7 +8394,7 @@
         <v>67</v>
       </c>
       <c r="I246">
-        <v>80</v>
+        <v>74</v>
       </c>
       <c r="J246">
         <v>0</v>
@@ -8402,7 +8402,7 @@
     </row>
     <row r="247" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A247" s="1">
-        <v>45480</v>
+        <v>45479</v>
       </c>
       <c r="B247">
         <v>2024</v>
@@ -8414,16 +8414,16 @@
         <v>11</v>
       </c>
       <c r="E247" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="F247" t="s">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="G247" t="s">
         <v>26</v>
       </c>
       <c r="H247">
-        <v>80</v>
+        <v>74</v>
       </c>
       <c r="I247">
         <v>67</v>
@@ -8446,19 +8446,19 @@
         <v>11</v>
       </c>
       <c r="E248" t="s">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="F248" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="G248" t="s">
         <v>25</v>
       </c>
       <c r="H248">
-        <v>84</v>
+        <v>67</v>
       </c>
       <c r="I248">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="J248">
         <v>0</v>
@@ -8478,19 +8478,19 @@
         <v>11</v>
       </c>
       <c r="E249" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="F249" t="s">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="G249" t="s">
         <v>26</v>
       </c>
       <c r="H249">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="I249">
-        <v>84</v>
+        <v>67</v>
       </c>
       <c r="J249">
         <v>0</v>
@@ -8510,19 +8510,19 @@
         <v>11</v>
       </c>
       <c r="E250" t="s">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="F250" t="s">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="G250" t="s">
         <v>25</v>
       </c>
       <c r="H250">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="I250">
-        <v>104</v>
+        <v>78</v>
       </c>
       <c r="J250">
         <v>0</v>
@@ -8542,19 +8542,19 @@
         <v>11</v>
       </c>
       <c r="E251" t="s">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="F251" t="s">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="G251" t="s">
         <v>26</v>
       </c>
       <c r="H251">
-        <v>104</v>
+        <v>78</v>
       </c>
       <c r="I251">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="J251">
         <v>0</v>
@@ -8574,19 +8574,19 @@
         <v>11</v>
       </c>
       <c r="E252" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="F252" t="s">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="G252" t="s">
         <v>25</v>
       </c>
       <c r="H252">
-        <v>71</v>
+        <v>85</v>
       </c>
       <c r="I252">
-        <v>84</v>
+        <v>104</v>
       </c>
       <c r="J252">
         <v>0</v>
@@ -8606,19 +8606,19 @@
         <v>11</v>
       </c>
       <c r="E253" t="s">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="F253" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="G253" t="s">
         <v>26</v>
       </c>
       <c r="H253">
-        <v>84</v>
+        <v>104</v>
       </c>
       <c r="I253">
-        <v>71</v>
+        <v>85</v>
       </c>
       <c r="J253">
         <v>0</v>
@@ -8626,7 +8626,7 @@
     </row>
     <row r="254" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A254" s="1">
-        <v>45482</v>
+        <v>45480</v>
       </c>
       <c r="B254">
         <v>2024</v>
@@ -8638,19 +8638,19 @@
         <v>11</v>
       </c>
       <c r="E254" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="F254" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="G254" t="s">
         <v>25</v>
       </c>
       <c r="H254">
-        <v>82</v>
+        <v>71</v>
       </c>
       <c r="I254">
-        <v>67</v>
+        <v>84</v>
       </c>
       <c r="J254">
         <v>0</v>
@@ -8658,7 +8658,7 @@
     </row>
     <row r="255" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A255" s="1">
-        <v>45482</v>
+        <v>45480</v>
       </c>
       <c r="B255">
         <v>2024</v>
@@ -8670,19 +8670,19 @@
         <v>11</v>
       </c>
       <c r="E255" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="F255" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="G255" t="s">
         <v>26</v>
       </c>
       <c r="H255">
-        <v>67</v>
+        <v>84</v>
       </c>
       <c r="I255">
-        <v>82</v>
+        <v>71</v>
       </c>
       <c r="J255">
         <v>0</v>
@@ -8690,7 +8690,7 @@
     </row>
     <row r="256" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A256" s="1">
-        <v>45483</v>
+        <v>45482</v>
       </c>
       <c r="B256">
         <v>2024</v>
@@ -8702,19 +8702,19 @@
         <v>11</v>
       </c>
       <c r="E256" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="F256" t="s">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="G256" t="s">
         <v>25</v>
       </c>
       <c r="H256">
-        <v>69</v>
+        <v>82</v>
       </c>
       <c r="I256">
-        <v>78</v>
+        <v>67</v>
       </c>
       <c r="J256">
         <v>0</v>
@@ -8722,7 +8722,7 @@
     </row>
     <row r="257" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A257" s="1">
-        <v>45483</v>
+        <v>45482</v>
       </c>
       <c r="B257">
         <v>2024</v>
@@ -8734,19 +8734,19 @@
         <v>11</v>
       </c>
       <c r="E257" t="s">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="F257" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="G257" t="s">
         <v>26</v>
       </c>
       <c r="H257">
-        <v>78</v>
+        <v>67</v>
       </c>
       <c r="I257">
-        <v>69</v>
+        <v>82</v>
       </c>
       <c r="J257">
         <v>0</v>
@@ -8766,19 +8766,19 @@
         <v>11</v>
       </c>
       <c r="E258" t="s">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="F258" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G258" t="s">
         <v>25</v>
       </c>
       <c r="H258">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="I258">
-        <v>68</v>
+        <v>78</v>
       </c>
       <c r="J258">
         <v>0</v>
@@ -8798,19 +8798,19 @@
         <v>11</v>
       </c>
       <c r="E259" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F259" t="s">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="G259" t="s">
         <v>26</v>
       </c>
       <c r="H259">
-        <v>68</v>
+        <v>78</v>
       </c>
       <c r="I259">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="J259">
         <v>0</v>
@@ -8830,19 +8830,19 @@
         <v>11</v>
       </c>
       <c r="E260" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F260" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G260" t="s">
         <v>25</v>
       </c>
       <c r="H260">
-        <v>89</v>
+        <v>71</v>
       </c>
       <c r="I260">
-        <v>84</v>
+        <v>68</v>
       </c>
       <c r="J260">
         <v>0</v>
@@ -8862,19 +8862,19 @@
         <v>11</v>
       </c>
       <c r="E261" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F261" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G261" t="s">
         <v>26</v>
       </c>
       <c r="H261">
-        <v>84</v>
+        <v>68</v>
       </c>
       <c r="I261">
-        <v>89</v>
+        <v>71</v>
       </c>
       <c r="J261">
         <v>0</v>
@@ -8894,19 +8894,19 @@
         <v>11</v>
       </c>
       <c r="E262" t="s">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="F262" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="G262" t="s">
         <v>25</v>
       </c>
       <c r="H262">
+        <v>89</v>
+      </c>
+      <c r="I262">
         <v>84</v>
-      </c>
-      <c r="I262">
-        <v>100</v>
       </c>
       <c r="J262">
         <v>0</v>
@@ -8926,19 +8926,19 @@
         <v>11</v>
       </c>
       <c r="E263" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="F263" t="s">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="G263" t="s">
         <v>26</v>
       </c>
       <c r="H263">
-        <v>100</v>
+        <v>84</v>
       </c>
       <c r="I263">
-        <v>84</v>
+        <v>89</v>
       </c>
       <c r="J263">
         <v>0</v>
@@ -8958,10 +8958,10 @@
         <v>11</v>
       </c>
       <c r="E264" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="F264" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="G264" t="s">
         <v>25</v>
@@ -8970,7 +8970,7 @@
         <v>84</v>
       </c>
       <c r="I264">
-        <v>79</v>
+        <v>100</v>
       </c>
       <c r="J264">
         <v>0</v>
@@ -8990,16 +8990,16 @@
         <v>11</v>
       </c>
       <c r="E265" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="F265" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="G265" t="s">
         <v>26</v>
       </c>
       <c r="H265">
-        <v>79</v>
+        <v>100</v>
       </c>
       <c r="I265">
         <v>84</v>
@@ -9010,7 +9010,7 @@
     </row>
     <row r="266" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A266" s="1">
-        <v>45484</v>
+        <v>45483</v>
       </c>
       <c r="B266">
         <v>2024</v>
@@ -9022,19 +9022,19 @@
         <v>11</v>
       </c>
       <c r="E266" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="F266" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="G266" t="s">
         <v>25</v>
       </c>
       <c r="H266">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="I266">
-        <v>91</v>
+        <v>79</v>
       </c>
       <c r="J266">
         <v>0</v>
@@ -9042,7 +9042,7 @@
     </row>
     <row r="267" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A267" s="1">
-        <v>45484</v>
+        <v>45483</v>
       </c>
       <c r="B267">
         <v>2024</v>
@@ -9054,19 +9054,19 @@
         <v>11</v>
       </c>
       <c r="E267" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="F267" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="G267" t="s">
         <v>26</v>
       </c>
       <c r="H267">
-        <v>91</v>
+        <v>79</v>
       </c>
       <c r="I267">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="J267">
         <v>0</v>
@@ -9074,7 +9074,7 @@
     </row>
     <row r="268" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A268" s="1">
-        <v>45485</v>
+        <v>45484</v>
       </c>
       <c r="B268">
         <v>2024</v>
@@ -9086,19 +9086,19 @@
         <v>11</v>
       </c>
       <c r="E268" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="F268" t="s">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="G268" t="s">
         <v>25</v>
       </c>
       <c r="H268">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="I268">
-        <v>70</v>
+        <v>91</v>
       </c>
       <c r="J268">
         <v>0</v>
@@ -9106,7 +9106,7 @@
     </row>
     <row r="269" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A269" s="1">
-        <v>45485</v>
+        <v>45484</v>
       </c>
       <c r="B269">
         <v>2024</v>
@@ -9118,19 +9118,19 @@
         <v>11</v>
       </c>
       <c r="E269" t="s">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="F269" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="G269" t="s">
         <v>26</v>
       </c>
       <c r="H269">
-        <v>70</v>
+        <v>91</v>
       </c>
       <c r="I269">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="J269">
         <v>0</v>
@@ -9150,19 +9150,19 @@
         <v>11</v>
       </c>
       <c r="E270" t="s">
-        <v>14</v>
+        <v>24</v>
       </c>
       <c r="F270" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="G270" t="s">
         <v>25</v>
       </c>
       <c r="H270">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="I270">
-        <v>95</v>
+        <v>70</v>
       </c>
       <c r="J270">
         <v>0</v>
@@ -9182,19 +9182,19 @@
         <v>11</v>
       </c>
       <c r="E271" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="F271" t="s">
-        <v>14</v>
+        <v>24</v>
       </c>
       <c r="G271" t="s">
         <v>26</v>
       </c>
       <c r="H271">
-        <v>95</v>
+        <v>70</v>
       </c>
       <c r="I271">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="J271">
         <v>0</v>
@@ -9214,19 +9214,19 @@
         <v>11</v>
       </c>
       <c r="E272" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="F272" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="G272" t="s">
         <v>25</v>
       </c>
       <c r="H272">
-        <v>63</v>
+        <v>86</v>
       </c>
       <c r="I272">
-        <v>91</v>
+        <v>95</v>
       </c>
       <c r="J272">
         <v>0</v>
@@ -9246,19 +9246,19 @@
         <v>11</v>
       </c>
       <c r="E273" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F273" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="G273" t="s">
         <v>26</v>
       </c>
       <c r="H273">
-        <v>91</v>
+        <v>95</v>
       </c>
       <c r="I273">
-        <v>63</v>
+        <v>86</v>
       </c>
       <c r="J273">
         <v>0</v>
@@ -9266,7 +9266,7 @@
     </row>
     <row r="274" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A274" s="1">
-        <v>45486</v>
+        <v>45485</v>
       </c>
       <c r="B274">
         <v>2024</v>
@@ -9278,19 +9278,19 @@
         <v>11</v>
       </c>
       <c r="E274" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="F274" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="G274" t="s">
         <v>25</v>
       </c>
       <c r="H274">
-        <v>81</v>
+        <v>63</v>
       </c>
       <c r="I274">
-        <v>67</v>
+        <v>91</v>
       </c>
       <c r="J274">
         <v>0</v>
@@ -9298,7 +9298,7 @@
     </row>
     <row r="275" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A275" s="1">
-        <v>45486</v>
+        <v>45485</v>
       </c>
       <c r="B275">
         <v>2024</v>
@@ -9310,19 +9310,19 @@
         <v>11</v>
       </c>
       <c r="E275" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="F275" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="G275" t="s">
         <v>26</v>
       </c>
       <c r="H275">
-        <v>67</v>
+        <v>91</v>
       </c>
       <c r="I275">
-        <v>81</v>
+        <v>63</v>
       </c>
       <c r="J275">
         <v>0</v>
@@ -9342,19 +9342,19 @@
         <v>11</v>
       </c>
       <c r="E276" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="F276" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="G276" t="s">
         <v>25</v>
       </c>
       <c r="H276">
-        <v>87</v>
+        <v>81</v>
       </c>
       <c r="I276">
-        <v>81</v>
+        <v>67</v>
       </c>
       <c r="J276">
         <v>0</v>
@@ -9374,19 +9374,19 @@
         <v>11</v>
       </c>
       <c r="E277" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="F277" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="G277" t="s">
         <v>26</v>
       </c>
       <c r="H277">
+        <v>67</v>
+      </c>
+      <c r="I277">
         <v>81</v>
-      </c>
-      <c r="I277">
-        <v>87</v>
       </c>
       <c r="J277">
         <v>0</v>
@@ -9394,7 +9394,7 @@
     </row>
     <row r="278" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A278" s="1">
-        <v>45487</v>
+        <v>45486</v>
       </c>
       <c r="B278">
         <v>2024</v>
@@ -9406,19 +9406,19 @@
         <v>11</v>
       </c>
       <c r="E278" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F278" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="G278" t="s">
         <v>25</v>
       </c>
       <c r="H278">
-        <v>69</v>
+        <v>87</v>
       </c>
       <c r="I278">
-        <v>96</v>
+        <v>81</v>
       </c>
       <c r="J278">
         <v>0</v>
@@ -9426,7 +9426,7 @@
     </row>
     <row r="279" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A279" s="1">
-        <v>45487</v>
+        <v>45486</v>
       </c>
       <c r="B279">
         <v>2024</v>
@@ -9438,19 +9438,19 @@
         <v>11</v>
       </c>
       <c r="E279" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="F279" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G279" t="s">
         <v>26</v>
       </c>
       <c r="H279">
-        <v>96</v>
+        <v>81</v>
       </c>
       <c r="I279">
-        <v>69</v>
+        <v>87</v>
       </c>
       <c r="J279">
         <v>0</v>
@@ -9470,19 +9470,19 @@
         <v>11</v>
       </c>
       <c r="E280" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="F280" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="G280" t="s">
         <v>25</v>
       </c>
       <c r="H280">
-        <v>81</v>
+        <v>69</v>
       </c>
       <c r="I280">
-        <v>74</v>
+        <v>96</v>
       </c>
       <c r="J280">
         <v>0</v>
@@ -9502,19 +9502,19 @@
         <v>11</v>
       </c>
       <c r="E281" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="F281" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="G281" t="s">
         <v>26</v>
       </c>
       <c r="H281">
-        <v>74</v>
+        <v>96</v>
       </c>
       <c r="I281">
-        <v>81</v>
+        <v>69</v>
       </c>
       <c r="J281">
         <v>0</v>
@@ -9534,19 +9534,19 @@
         <v>11</v>
       </c>
       <c r="E282" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="F282" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="G282" t="s">
         <v>25</v>
       </c>
       <c r="H282">
-        <v>70</v>
+        <v>81</v>
       </c>
       <c r="I282">
-        <v>81</v>
+        <v>74</v>
       </c>
       <c r="J282">
         <v>0</v>
@@ -9566,19 +9566,19 @@
         <v>11</v>
       </c>
       <c r="E283" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="F283" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="G283" t="s">
         <v>26</v>
       </c>
       <c r="H283">
+        <v>74</v>
+      </c>
+      <c r="I283">
         <v>81</v>
-      </c>
-      <c r="I283">
-        <v>70</v>
       </c>
       <c r="J283">
         <v>0</v>
@@ -9598,19 +9598,19 @@
         <v>11</v>
       </c>
       <c r="E284" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="F284" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="G284" t="s">
         <v>25</v>
       </c>
       <c r="H284">
-        <v>89</v>
+        <v>70</v>
       </c>
       <c r="I284">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="J284">
         <v>0</v>
@@ -9630,19 +9630,19 @@
         <v>11</v>
       </c>
       <c r="E285" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="F285" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="G285" t="s">
         <v>26</v>
       </c>
       <c r="H285">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="I285">
-        <v>89</v>
+        <v>70</v>
       </c>
       <c r="J285">
         <v>0</v>
@@ -9650,7 +9650,7 @@
     </row>
     <row r="286" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A286" s="1">
-        <v>45489</v>
+        <v>45487</v>
       </c>
       <c r="B286">
         <v>2024</v>
@@ -9662,10 +9662,10 @@
         <v>11</v>
       </c>
       <c r="E286" t="s">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="F286" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="G286" t="s">
         <v>25</v>
@@ -9674,7 +9674,7 @@
         <v>89</v>
       </c>
       <c r="I286">
-        <v>83</v>
+        <v>77</v>
       </c>
       <c r="J286">
         <v>0</v>
@@ -9682,7 +9682,7 @@
     </row>
     <row r="287" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A287" s="1">
-        <v>45489</v>
+        <v>45487</v>
       </c>
       <c r="B287">
         <v>2024</v>
@@ -9694,16 +9694,16 @@
         <v>11</v>
       </c>
       <c r="E287" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="F287" t="s">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="G287" t="s">
         <v>26</v>
       </c>
       <c r="H287">
-        <v>83</v>
+        <v>77</v>
       </c>
       <c r="I287">
         <v>89</v>
@@ -9726,19 +9726,19 @@
         <v>11</v>
       </c>
       <c r="E288" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="F288" t="s">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="G288" t="s">
         <v>25</v>
       </c>
       <c r="H288">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="I288">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="J288">
         <v>0</v>
@@ -9758,19 +9758,19 @@
         <v>11</v>
       </c>
       <c r="E289" t="s">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="F289" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="G289" t="s">
         <v>26</v>
       </c>
       <c r="H289">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="I289">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="J289">
         <v>0</v>
@@ -9790,19 +9790,19 @@
         <v>11</v>
       </c>
       <c r="E290" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F290" t="s">
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="G290" t="s">
         <v>25</v>
       </c>
       <c r="H290">
-        <v>74</v>
+        <v>93</v>
       </c>
       <c r="I290">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="J290">
         <v>0</v>
@@ -9822,19 +9822,19 @@
         <v>11</v>
       </c>
       <c r="E291" t="s">
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="F291" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G291" t="s">
         <v>26</v>
       </c>
       <c r="H291">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="I291">
-        <v>74</v>
+        <v>93</v>
       </c>
       <c r="J291">
         <v>0</v>
@@ -9854,19 +9854,19 @@
         <v>11</v>
       </c>
       <c r="E292" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="F292" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G292" t="s">
         <v>25</v>
       </c>
       <c r="H292">
-        <v>96</v>
+        <v>74</v>
       </c>
       <c r="I292">
-        <v>87</v>
+        <v>82</v>
       </c>
       <c r="J292">
         <v>0</v>
@@ -9886,19 +9886,19 @@
         <v>11</v>
       </c>
       <c r="E293" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F293" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="G293" t="s">
         <v>26</v>
       </c>
       <c r="H293">
-        <v>87</v>
+        <v>82</v>
       </c>
       <c r="I293">
-        <v>96</v>
+        <v>74</v>
       </c>
       <c r="J293">
         <v>0</v>
@@ -9906,7 +9906,7 @@
     </row>
     <row r="294" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A294" s="1">
-        <v>45490</v>
+        <v>45489</v>
       </c>
       <c r="B294">
         <v>2024</v>
@@ -9918,19 +9918,19 @@
         <v>11</v>
       </c>
       <c r="E294" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="F294" t="s">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="G294" t="s">
         <v>25</v>
       </c>
       <c r="H294">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="I294">
-        <v>101</v>
+        <v>87</v>
       </c>
       <c r="J294">
         <v>0</v>
@@ -9938,7 +9938,7 @@
     </row>
     <row r="295" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A295" s="1">
-        <v>45490</v>
+        <v>45489</v>
       </c>
       <c r="B295">
         <v>2024</v>
@@ -9950,19 +9950,19 @@
         <v>11</v>
       </c>
       <c r="E295" t="s">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="F295" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="G295" t="s">
         <v>26</v>
       </c>
       <c r="H295">
-        <v>101</v>
+        <v>87</v>
       </c>
       <c r="I295">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="J295">
         <v>0</v>
@@ -9982,19 +9982,19 @@
         <v>11</v>
       </c>
       <c r="E296" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="F296" t="s">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="G296" t="s">
         <v>25</v>
       </c>
       <c r="H296">
-        <v>79</v>
+        <v>93</v>
       </c>
       <c r="I296">
-        <v>86</v>
+        <v>101</v>
       </c>
       <c r="J296">
         <v>0</v>
@@ -10014,19 +10014,19 @@
         <v>11</v>
       </c>
       <c r="E297" t="s">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="F297" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="G297" t="s">
         <v>26</v>
       </c>
       <c r="H297">
-        <v>86</v>
+        <v>101</v>
       </c>
       <c r="I297">
-        <v>79</v>
+        <v>93</v>
       </c>
       <c r="J297">
         <v>0</v>
@@ -10034,7 +10034,7 @@
     </row>
     <row r="298" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A298" s="1">
-        <v>45519</v>
+        <v>45490</v>
       </c>
       <c r="B298">
         <v>2024</v>
@@ -10046,19 +10046,19 @@
         <v>11</v>
       </c>
       <c r="E298" t="s">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="F298" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="G298" t="s">
         <v>25</v>
       </c>
       <c r="H298">
-        <v>85</v>
+        <v>79</v>
       </c>
       <c r="I298">
-        <v>65</v>
+        <v>86</v>
       </c>
       <c r="J298">
         <v>0</v>
@@ -10066,7 +10066,7 @@
     </row>
     <row r="299" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A299" s="1">
-        <v>45519</v>
+        <v>45490</v>
       </c>
       <c r="B299">
         <v>2024</v>
@@ -10078,19 +10078,19 @@
         <v>11</v>
       </c>
       <c r="E299" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="F299" t="s">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="G299" t="s">
         <v>26</v>
       </c>
       <c r="H299">
-        <v>65</v>
+        <v>86</v>
       </c>
       <c r="I299">
-        <v>85</v>
+        <v>79</v>
       </c>
       <c r="J299">
         <v>0</v>
@@ -10110,19 +10110,19 @@
         <v>11</v>
       </c>
       <c r="E300" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F300" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="G300" t="s">
         <v>25</v>
       </c>
       <c r="H300">
-        <v>103</v>
+        <v>85</v>
       </c>
       <c r="I300">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="J300">
         <v>0</v>
@@ -10142,19 +10142,19 @@
         <v>11</v>
       </c>
       <c r="E301" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="F301" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G301" t="s">
         <v>26</v>
       </c>
       <c r="H301">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="I301">
-        <v>103</v>
+        <v>85</v>
       </c>
       <c r="J301">
         <v>0</v>
@@ -10174,19 +10174,19 @@
         <v>11</v>
       </c>
       <c r="E302" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F302" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G302" t="s">
         <v>25</v>
       </c>
       <c r="H302">
+        <v>103</v>
+      </c>
+      <c r="I302">
         <v>68</v>
-      </c>
-      <c r="I302">
-        <v>79</v>
       </c>
       <c r="J302">
         <v>0</v>
@@ -10206,19 +10206,19 @@
         <v>11</v>
       </c>
       <c r="E303" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="F303" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G303" t="s">
         <v>26</v>
       </c>
       <c r="H303">
-        <v>79</v>
+        <v>68</v>
       </c>
       <c r="I303">
-        <v>68</v>
+        <v>103</v>
       </c>
       <c r="J303">
         <v>0</v>
@@ -10226,7 +10226,7 @@
     </row>
     <row r="304" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A304" s="1">
-        <v>45520</v>
+        <v>45519</v>
       </c>
       <c r="B304">
         <v>2024</v>
@@ -10238,19 +10238,19 @@
         <v>11</v>
       </c>
       <c r="E304" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="F304" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="G304" t="s">
         <v>25</v>
       </c>
       <c r="H304">
-        <v>81</v>
+        <v>68</v>
       </c>
       <c r="I304">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="J304">
         <v>0</v>
@@ -10258,7 +10258,7 @@
     </row>
     <row r="305" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A305" s="1">
-        <v>45520</v>
+        <v>45519</v>
       </c>
       <c r="B305">
         <v>2024</v>
@@ -10270,19 +10270,19 @@
         <v>11</v>
       </c>
       <c r="E305" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="F305" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="G305" t="s">
         <v>26</v>
       </c>
       <c r="H305">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="I305">
-        <v>81</v>
+        <v>68</v>
       </c>
       <c r="J305">
         <v>0</v>
@@ -10302,19 +10302,19 @@
         <v>11</v>
       </c>
       <c r="E306" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="F306" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="G306" t="s">
         <v>25</v>
       </c>
       <c r="H306">
-        <v>109</v>
+        <v>81</v>
       </c>
       <c r="I306">
-        <v>91</v>
+        <v>83</v>
       </c>
       <c r="J306">
         <v>0</v>
@@ -10334,19 +10334,19 @@
         <v>11</v>
       </c>
       <c r="E307" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F307" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="G307" t="s">
         <v>26</v>
       </c>
       <c r="H307">
-        <v>91</v>
+        <v>83</v>
       </c>
       <c r="I307">
-        <v>109</v>
+        <v>81</v>
       </c>
       <c r="J307">
         <v>0</v>
@@ -10366,19 +10366,19 @@
         <v>11</v>
       </c>
       <c r="E308" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="F308" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="G308" t="s">
         <v>25</v>
       </c>
       <c r="H308">
-        <v>89</v>
+        <v>109</v>
       </c>
       <c r="I308">
-        <v>98</v>
+        <v>91</v>
       </c>
       <c r="J308">
         <v>0</v>
@@ -10398,19 +10398,19 @@
         <v>11</v>
       </c>
       <c r="E309" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="F309" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="G309" t="s">
         <v>26</v>
       </c>
       <c r="H309">
-        <v>98</v>
+        <v>91</v>
       </c>
       <c r="I309">
-        <v>89</v>
+        <v>109</v>
       </c>
       <c r="J309">
         <v>0</v>
@@ -10418,7 +10418,7 @@
     </row>
     <row r="310" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A310" s="1">
-        <v>45521</v>
+        <v>45520</v>
       </c>
       <c r="B310">
         <v>2024</v>
@@ -10430,19 +10430,19 @@
         <v>11</v>
       </c>
       <c r="E310" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="F310" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="G310" t="s">
         <v>25</v>
       </c>
       <c r="H310">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="I310">
-        <v>86</v>
+        <v>98</v>
       </c>
       <c r="J310">
         <v>0</v>
@@ -10450,7 +10450,7 @@
     </row>
     <row r="311" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A311" s="1">
-        <v>45521</v>
+        <v>45520</v>
       </c>
       <c r="B311">
         <v>2024</v>
@@ -10462,19 +10462,19 @@
         <v>11</v>
       </c>
       <c r="E311" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="F311" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="G311" t="s">
         <v>26</v>
       </c>
       <c r="H311">
-        <v>86</v>
+        <v>98</v>
       </c>
       <c r="I311">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="J311">
         <v>0</v>
@@ -10494,19 +10494,19 @@
         <v>11</v>
       </c>
       <c r="E312" t="s">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="F312" t="s">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="G312" t="s">
         <v>25</v>
       </c>
       <c r="H312">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="I312">
-        <v>67</v>
+        <v>86</v>
       </c>
       <c r="J312">
         <v>0</v>
@@ -10526,19 +10526,19 @@
         <v>11</v>
       </c>
       <c r="E313" t="s">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="F313" t="s">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="G313" t="s">
         <v>26</v>
       </c>
       <c r="H313">
-        <v>67</v>
+        <v>86</v>
       </c>
       <c r="I313">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="J313">
         <v>0</v>
@@ -10558,19 +10558,19 @@
         <v>11</v>
       </c>
       <c r="E314" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="F314" t="s">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="G314" t="s">
         <v>25</v>
       </c>
       <c r="H314">
-        <v>99</v>
+        <v>79</v>
       </c>
       <c r="I314">
-        <v>83</v>
+        <v>67</v>
       </c>
       <c r="J314">
         <v>0</v>
@@ -10590,19 +10590,19 @@
         <v>11</v>
       </c>
       <c r="E315" t="s">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="F315" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="G315" t="s">
         <v>26</v>
       </c>
       <c r="H315">
-        <v>83</v>
+        <v>67</v>
       </c>
       <c r="I315">
-        <v>99</v>
+        <v>79</v>
       </c>
       <c r="J315">
         <v>0</v>
@@ -10610,7 +10610,7 @@
     </row>
     <row r="316" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A316" s="1">
-        <v>45522</v>
+        <v>45521</v>
       </c>
       <c r="B316">
         <v>2024</v>
@@ -10622,19 +10622,19 @@
         <v>11</v>
       </c>
       <c r="E316" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="F316" t="s">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="G316" t="s">
         <v>25</v>
       </c>
       <c r="H316">
-        <v>70</v>
+        <v>99</v>
       </c>
       <c r="I316">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="J316">
         <v>0</v>
@@ -10642,7 +10642,7 @@
     </row>
     <row r="317" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A317" s="1">
-        <v>45522</v>
+        <v>45521</v>
       </c>
       <c r="B317">
         <v>2024</v>
@@ -10654,19 +10654,19 @@
         <v>11</v>
       </c>
       <c r="E317" t="s">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="F317" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="G317" t="s">
         <v>26</v>
       </c>
       <c r="H317">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="I317">
-        <v>70</v>
+        <v>99</v>
       </c>
       <c r="J317">
         <v>0</v>
@@ -10686,19 +10686,19 @@
         <v>11</v>
       </c>
       <c r="E318" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="F318" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="G318" t="s">
         <v>25</v>
       </c>
       <c r="H318">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="I318">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="J318">
         <v>0</v>
@@ -10718,19 +10718,19 @@
         <v>11</v>
       </c>
       <c r="E319" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="F319" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="G319" t="s">
         <v>26</v>
       </c>
       <c r="H319">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="I319">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="J319">
         <v>0</v>
@@ -10750,19 +10750,19 @@
         <v>11</v>
       </c>
       <c r="E320" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="F320" t="s">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="G320" t="s">
         <v>25</v>
       </c>
       <c r="H320">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="I320">
-        <v>87</v>
+        <v>92</v>
       </c>
       <c r="J320">
         <v>0</v>
@@ -10782,19 +10782,19 @@
         <v>11</v>
       </c>
       <c r="E321" t="s">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="F321" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="G321" t="s">
         <v>26</v>
       </c>
       <c r="H321">
-        <v>87</v>
+        <v>92</v>
       </c>
       <c r="I321">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="J321">
         <v>0</v>
@@ -10814,19 +10814,19 @@
         <v>11</v>
       </c>
       <c r="E322" t="s">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="F322" t="s">
-        <v>14</v>
+        <v>24</v>
       </c>
       <c r="G322" t="s">
         <v>25</v>
       </c>
       <c r="H322">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="I322">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="J322">
         <v>0</v>
@@ -10846,19 +10846,19 @@
         <v>11</v>
       </c>
       <c r="E323" t="s">
-        <v>14</v>
+        <v>24</v>
       </c>
       <c r="F323" t="s">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="G323" t="s">
         <v>26</v>
       </c>
       <c r="H323">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="I323">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="J323">
         <v>0</v>
@@ -10866,7 +10866,7 @@
     </row>
     <row r="324" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A324" s="1">
-        <v>45524</v>
+        <v>45522</v>
       </c>
       <c r="B324">
         <v>2024</v>
@@ -10878,19 +10878,19 @@
         <v>11</v>
       </c>
       <c r="E324" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="F324" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="G324" t="s">
         <v>25</v>
       </c>
       <c r="H324">
-        <v>61</v>
+        <v>68</v>
       </c>
       <c r="I324">
-        <v>69</v>
+        <v>86</v>
       </c>
       <c r="J324">
         <v>0</v>
@@ -10898,7 +10898,7 @@
     </row>
     <row r="325" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A325" s="1">
-        <v>45524</v>
+        <v>45522</v>
       </c>
       <c r="B325">
         <v>2024</v>
@@ -10910,19 +10910,19 @@
         <v>11</v>
       </c>
       <c r="E325" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="F325" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="G325" t="s">
         <v>26</v>
       </c>
       <c r="H325">
-        <v>69</v>
+        <v>86</v>
       </c>
       <c r="I325">
-        <v>61</v>
+        <v>68</v>
       </c>
       <c r="J325">
         <v>0</v>
@@ -10942,19 +10942,19 @@
         <v>11</v>
       </c>
       <c r="E326" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="F326" t="s">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="G326" t="s">
         <v>25</v>
       </c>
       <c r="H326">
-        <v>74</v>
+        <v>61</v>
       </c>
       <c r="I326">
-        <v>94</v>
+        <v>69</v>
       </c>
       <c r="J326">
         <v>0</v>
@@ -10974,19 +10974,19 @@
         <v>11</v>
       </c>
       <c r="E327" t="s">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="F327" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="G327" t="s">
         <v>26</v>
       </c>
       <c r="H327">
-        <v>94</v>
+        <v>69</v>
       </c>
       <c r="I327">
-        <v>74</v>
+        <v>61</v>
       </c>
       <c r="J327">
         <v>0</v>
@@ -11006,19 +11006,19 @@
         <v>11</v>
       </c>
       <c r="E328" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="F328" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G328" t="s">
         <v>25</v>
       </c>
       <c r="H328">
-        <v>83</v>
+        <v>74</v>
       </c>
       <c r="I328">
-        <v>77</v>
+        <v>94</v>
       </c>
       <c r="J328">
         <v>0</v>
@@ -11038,19 +11038,19 @@
         <v>11</v>
       </c>
       <c r="E329" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F329" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="G329" t="s">
         <v>26</v>
       </c>
       <c r="H329">
-        <v>77</v>
+        <v>94</v>
       </c>
       <c r="I329">
-        <v>83</v>
+        <v>74</v>
       </c>
       <c r="J329">
         <v>0</v>
@@ -11058,7 +11058,7 @@
     </row>
     <row r="330" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A330" s="1">
-        <v>45525</v>
+        <v>45524</v>
       </c>
       <c r="B330">
         <v>2024</v>
@@ -11070,19 +11070,19 @@
         <v>11</v>
       </c>
       <c r="E330" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="F330" t="s">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="G330" t="s">
         <v>25</v>
       </c>
       <c r="H330">
-        <v>63</v>
+        <v>83</v>
       </c>
       <c r="I330">
-        <v>72</v>
+        <v>77</v>
       </c>
       <c r="J330">
         <v>0</v>
@@ -11090,7 +11090,7 @@
     </row>
     <row r="331" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A331" s="1">
-        <v>45525</v>
+        <v>45524</v>
       </c>
       <c r="B331">
         <v>2024</v>
@@ -11102,19 +11102,19 @@
         <v>11</v>
       </c>
       <c r="E331" t="s">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="F331" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="G331" t="s">
         <v>26</v>
       </c>
       <c r="H331">
-        <v>72</v>
+        <v>77</v>
       </c>
       <c r="I331">
-        <v>63</v>
+        <v>83</v>
       </c>
       <c r="J331">
         <v>0</v>
@@ -11134,19 +11134,19 @@
         <v>11</v>
       </c>
       <c r="E332" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="F332" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="G332" t="s">
         <v>25</v>
       </c>
       <c r="H332">
-        <v>98</v>
+        <v>63</v>
       </c>
       <c r="I332">
-        <v>87</v>
+        <v>72</v>
       </c>
       <c r="J332">
         <v>0</v>
@@ -11166,19 +11166,19 @@
         <v>11</v>
       </c>
       <c r="E333" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="F333" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="G333" t="s">
         <v>26</v>
       </c>
       <c r="H333">
-        <v>87</v>
+        <v>72</v>
       </c>
       <c r="I333">
-        <v>98</v>
+        <v>63</v>
       </c>
       <c r="J333">
         <v>0</v>
@@ -11186,7 +11186,7 @@
     </row>
     <row r="334" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A334" s="1">
-        <v>45526</v>
+        <v>45525</v>
       </c>
       <c r="B334">
         <v>2024</v>
@@ -11198,19 +11198,19 @@
         <v>11</v>
       </c>
       <c r="E334" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="F334" t="s">
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="G334" t="s">
         <v>25</v>
       </c>
       <c r="H334">
-        <v>71</v>
+        <v>98</v>
       </c>
       <c r="I334">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="J334">
         <v>0</v>
@@ -11218,7 +11218,7 @@
     </row>
     <row r="335" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A335" s="1">
-        <v>45526</v>
+        <v>45525</v>
       </c>
       <c r="B335">
         <v>2024</v>
@@ -11230,19 +11230,19 @@
         <v>11</v>
       </c>
       <c r="E335" t="s">
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="F335" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="G335" t="s">
         <v>26</v>
       </c>
       <c r="H335">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="I335">
-        <v>71</v>
+        <v>98</v>
       </c>
       <c r="J335">
         <v>0</v>
@@ -11250,7 +11250,7 @@
     </row>
     <row r="336" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A336" s="1">
-        <v>45527</v>
+        <v>45526</v>
       </c>
       <c r="B336">
         <v>2024</v>
@@ -11262,19 +11262,19 @@
         <v>11</v>
       </c>
       <c r="E336" t="s">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="F336" t="s">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="G336" t="s">
         <v>25</v>
       </c>
       <c r="H336">
-        <v>82</v>
+        <v>71</v>
       </c>
       <c r="I336">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="J336">
         <v>0</v>
@@ -11282,7 +11282,7 @@
     </row>
     <row r="337" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A337" s="1">
-        <v>45527</v>
+        <v>45526</v>
       </c>
       <c r="B337">
         <v>2024</v>
@@ -11294,19 +11294,19 @@
         <v>11</v>
       </c>
       <c r="E337" t="s">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="F337" t="s">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="G337" t="s">
         <v>26</v>
       </c>
       <c r="H337">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="I337">
-        <v>82</v>
+        <v>71</v>
       </c>
       <c r="J337">
         <v>0</v>
@@ -11326,19 +11326,19 @@
         <v>11</v>
       </c>
       <c r="E338" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="F338" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="G338" t="s">
         <v>25</v>
       </c>
       <c r="H338">
+        <v>82</v>
+      </c>
+      <c r="I338">
         <v>80</v>
-      </c>
-      <c r="I338">
-        <v>82</v>
       </c>
       <c r="J338">
         <v>0</v>
@@ -11358,19 +11358,19 @@
         <v>11</v>
       </c>
       <c r="E339" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="F339" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="G339" t="s">
         <v>26</v>
       </c>
       <c r="H339">
+        <v>80</v>
+      </c>
+      <c r="I339">
         <v>82</v>
-      </c>
-      <c r="I339">
-        <v>80</v>
       </c>
       <c r="J339">
         <v>0</v>
@@ -11390,19 +11390,19 @@
         <v>11</v>
       </c>
       <c r="E340" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="F340" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="G340" t="s">
         <v>25</v>
       </c>
       <c r="H340">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="I340">
-        <v>87</v>
+        <v>82</v>
       </c>
       <c r="J340">
         <v>0</v>
@@ -11422,19 +11422,19 @@
         <v>11</v>
       </c>
       <c r="E341" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="F341" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="G341" t="s">
         <v>26</v>
       </c>
       <c r="H341">
-        <v>87</v>
+        <v>82</v>
       </c>
       <c r="I341">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="J341">
         <v>0</v>
@@ -11454,10 +11454,10 @@
         <v>11</v>
       </c>
       <c r="E342" t="s">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="F342" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="G342" t="s">
         <v>25</v>
@@ -11466,7 +11466,7 @@
         <v>74</v>
       </c>
       <c r="I342">
-        <v>80</v>
+        <v>87</v>
       </c>
       <c r="J342">
         <v>0</v>
@@ -11486,16 +11486,16 @@
         <v>11</v>
       </c>
       <c r="E343" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="F343" t="s">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="G343" t="s">
         <v>26</v>
       </c>
       <c r="H343">
-        <v>80</v>
+        <v>87</v>
       </c>
       <c r="I343">
         <v>74</v>
@@ -11506,7 +11506,7 @@
     </row>
     <row r="344" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A344" s="1">
-        <v>45528</v>
+        <v>45527</v>
       </c>
       <c r="B344">
         <v>2024</v>
@@ -11518,19 +11518,19 @@
         <v>11</v>
       </c>
       <c r="E344" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="F344" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="G344" t="s">
         <v>25</v>
       </c>
       <c r="H344">
+        <v>74</v>
+      </c>
+      <c r="I344">
         <v>80</v>
-      </c>
-      <c r="I344">
-        <v>90</v>
       </c>
       <c r="J344">
         <v>0</v>
@@ -11538,7 +11538,7 @@
     </row>
     <row r="345" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A345" s="1">
-        <v>45528</v>
+        <v>45527</v>
       </c>
       <c r="B345">
         <v>2024</v>
@@ -11550,19 +11550,19 @@
         <v>11</v>
       </c>
       <c r="E345" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="F345" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="G345" t="s">
         <v>26</v>
       </c>
       <c r="H345">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="I345">
-        <v>80</v>
+        <v>74</v>
       </c>
       <c r="J345">
         <v>0</v>
@@ -11582,19 +11582,19 @@
         <v>11</v>
       </c>
       <c r="E346" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="F346" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="G346" t="s">
         <v>25</v>
       </c>
       <c r="H346">
-        <v>72</v>
+        <v>80</v>
       </c>
       <c r="I346">
-        <v>64</v>
+        <v>90</v>
       </c>
       <c r="J346">
         <v>0</v>
@@ -11614,19 +11614,19 @@
         <v>11</v>
       </c>
       <c r="E347" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="F347" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="G347" t="s">
         <v>26</v>
       </c>
       <c r="H347">
-        <v>64</v>
+        <v>90</v>
       </c>
       <c r="I347">
-        <v>72</v>
+        <v>80</v>
       </c>
       <c r="J347">
         <v>0</v>
@@ -11634,7 +11634,7 @@
     </row>
     <row r="348" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A348" s="1">
-        <v>45529</v>
+        <v>45528</v>
       </c>
       <c r="B348">
         <v>2024</v>
@@ -11646,19 +11646,19 @@
         <v>11</v>
       </c>
       <c r="E348" t="s">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="F348" t="s">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="G348" t="s">
         <v>25</v>
       </c>
       <c r="H348">
-        <v>77</v>
+        <v>72</v>
       </c>
       <c r="I348">
-        <v>75</v>
+        <v>64</v>
       </c>
       <c r="J348">
         <v>0</v>
@@ -11666,7 +11666,7 @@
     </row>
     <row r="349" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A349" s="1">
-        <v>45529</v>
+        <v>45528</v>
       </c>
       <c r="B349">
         <v>2024</v>
@@ -11678,19 +11678,19 @@
         <v>11</v>
       </c>
       <c r="E349" t="s">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="F349" t="s">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="G349" t="s">
         <v>26</v>
       </c>
       <c r="H349">
-        <v>75</v>
+        <v>64</v>
       </c>
       <c r="I349">
-        <v>77</v>
+        <v>72</v>
       </c>
       <c r="J349">
         <v>0</v>
@@ -11710,19 +11710,19 @@
         <v>11</v>
       </c>
       <c r="E350" t="s">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="F350" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="G350" t="s">
         <v>25</v>
       </c>
       <c r="H350">
-        <v>110</v>
+        <v>77</v>
       </c>
       <c r="I350">
-        <v>113</v>
+        <v>75</v>
       </c>
       <c r="J350">
         <v>0</v>
@@ -11742,19 +11742,19 @@
         <v>11</v>
       </c>
       <c r="E351" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="F351" t="s">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="G351" t="s">
         <v>26</v>
       </c>
       <c r="H351">
-        <v>113</v>
+        <v>75</v>
       </c>
       <c r="I351">
-        <v>110</v>
+        <v>77</v>
       </c>
       <c r="J351">
         <v>0</v>
@@ -11762,7 +11762,7 @@
     </row>
     <row r="352" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A352" s="1">
-        <v>45530</v>
+        <v>45529</v>
       </c>
       <c r="B352">
         <v>2024</v>
@@ -11774,19 +11774,19 @@
         <v>11</v>
       </c>
       <c r="E352" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="F352" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="G352" t="s">
         <v>25</v>
       </c>
       <c r="H352">
-        <v>84</v>
+        <v>110</v>
       </c>
       <c r="I352">
-        <v>79</v>
+        <v>113</v>
       </c>
       <c r="J352">
         <v>0</v>
@@ -11794,7 +11794,7 @@
     </row>
     <row r="353" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A353" s="1">
-        <v>45530</v>
+        <v>45529</v>
       </c>
       <c r="B353">
         <v>2024</v>
@@ -11806,19 +11806,19 @@
         <v>11</v>
       </c>
       <c r="E353" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F353" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="G353" t="s">
         <v>26</v>
       </c>
       <c r="H353">
-        <v>79</v>
+        <v>113</v>
       </c>
       <c r="I353">
-        <v>84</v>
+        <v>110</v>
       </c>
       <c r="J353">
         <v>0</v>
@@ -11838,10 +11838,10 @@
         <v>11</v>
       </c>
       <c r="E354" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="F354" t="s">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="G354" t="s">
         <v>25</v>
@@ -11850,7 +11850,7 @@
         <v>84</v>
       </c>
       <c r="I354">
-        <v>70</v>
+        <v>79</v>
       </c>
       <c r="J354">
         <v>0</v>
@@ -11870,16 +11870,16 @@
         <v>11</v>
       </c>
       <c r="E355" t="s">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="F355" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="G355" t="s">
         <v>26</v>
       </c>
       <c r="H355">
-        <v>70</v>
+        <v>79</v>
       </c>
       <c r="I355">
         <v>84</v>
@@ -11902,19 +11902,19 @@
         <v>11</v>
       </c>
       <c r="E356" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F356" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="G356" t="s">
         <v>25</v>
       </c>
       <c r="H356">
-        <v>74</v>
+        <v>84</v>
       </c>
       <c r="I356">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="J356">
         <v>0</v>
@@ -11934,19 +11934,19 @@
         <v>11</v>
       </c>
       <c r="E357" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="F357" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G357" t="s">
         <v>26</v>
       </c>
       <c r="H357">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="I357">
-        <v>74</v>
+        <v>84</v>
       </c>
       <c r="J357">
         <v>0</v>
@@ -11954,7 +11954,7 @@
     </row>
     <row r="358" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A358" s="1">
-        <v>45531</v>
+        <v>45530</v>
       </c>
       <c r="B358">
         <v>2024</v>
@@ -11966,19 +11966,19 @@
         <v>11</v>
       </c>
       <c r="E358" t="s">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="F358" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="G358" t="s">
         <v>25</v>
       </c>
       <c r="H358">
-        <v>90</v>
+        <v>74</v>
       </c>
       <c r="I358">
-        <v>93</v>
+        <v>72</v>
       </c>
       <c r="J358">
         <v>0</v>
@@ -11986,7 +11986,7 @@
     </row>
     <row r="359" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A359" s="1">
-        <v>45531</v>
+        <v>45530</v>
       </c>
       <c r="B359">
         <v>2024</v>
@@ -11998,19 +11998,19 @@
         <v>11</v>
       </c>
       <c r="E359" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="F359" t="s">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="G359" t="s">
         <v>26</v>
       </c>
       <c r="H359">
-        <v>93</v>
+        <v>72</v>
       </c>
       <c r="I359">
-        <v>90</v>
+        <v>74</v>
       </c>
       <c r="J359">
         <v>0</v>
@@ -12018,7 +12018,7 @@
     </row>
     <row r="360" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A360" s="1">
-        <v>45532</v>
+        <v>45531</v>
       </c>
       <c r="B360">
         <v>2024</v>
@@ -12030,19 +12030,19 @@
         <v>11</v>
       </c>
       <c r="E360" t="s">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="F360" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="G360" t="s">
         <v>25</v>
       </c>
       <c r="H360">
-        <v>74</v>
+        <v>90</v>
       </c>
       <c r="I360">
-        <v>70</v>
+        <v>93</v>
       </c>
       <c r="J360">
         <v>0</v>
@@ -12050,7 +12050,7 @@
     </row>
     <row r="361" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A361" s="1">
-        <v>45532</v>
+        <v>45531</v>
       </c>
       <c r="B361">
         <v>2024</v>
@@ -12062,19 +12062,19 @@
         <v>11</v>
       </c>
       <c r="E361" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="F361" t="s">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="G361" t="s">
         <v>26</v>
       </c>
       <c r="H361">
-        <v>70</v>
+        <v>93</v>
       </c>
       <c r="I361">
-        <v>74</v>
+        <v>90</v>
       </c>
       <c r="J361">
         <v>0</v>
@@ -12094,19 +12094,19 @@
         <v>11</v>
       </c>
       <c r="E362" t="s">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="F362" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="G362" t="s">
         <v>25</v>
       </c>
       <c r="H362">
-        <v>80</v>
+        <v>74</v>
       </c>
       <c r="I362">
-        <v>84</v>
+        <v>70</v>
       </c>
       <c r="J362">
         <v>0</v>
@@ -12126,19 +12126,19 @@
         <v>11</v>
       </c>
       <c r="E363" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="F363" t="s">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="G363" t="s">
         <v>26</v>
       </c>
       <c r="H363">
-        <v>84</v>
+        <v>70</v>
       </c>
       <c r="I363">
-        <v>80</v>
+        <v>74</v>
       </c>
       <c r="J363">
         <v>0</v>
@@ -12158,19 +12158,19 @@
         <v>11</v>
       </c>
       <c r="E364" t="s">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="F364" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="G364" t="s">
         <v>25</v>
       </c>
       <c r="H364">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="I364">
-        <v>94</v>
+        <v>84</v>
       </c>
       <c r="J364">
         <v>0</v>
@@ -12190,19 +12190,19 @@
         <v>11</v>
       </c>
       <c r="E365" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="F365" t="s">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="G365" t="s">
         <v>26</v>
       </c>
       <c r="H365">
-        <v>94</v>
+        <v>84</v>
       </c>
       <c r="I365">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="J365">
         <v>0</v>
@@ -12222,19 +12222,19 @@
         <v>11</v>
       </c>
       <c r="E366" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="F366" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G366" t="s">
         <v>25</v>
       </c>
       <c r="H366">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="I366">
-        <v>76</v>
+        <v>94</v>
       </c>
       <c r="J366">
         <v>0</v>
@@ -12254,19 +12254,19 @@
         <v>11</v>
       </c>
       <c r="E367" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F367" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="G367" t="s">
         <v>26</v>
       </c>
       <c r="H367">
-        <v>76</v>
+        <v>94</v>
       </c>
       <c r="I367">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="J367">
         <v>0</v>
@@ -12286,19 +12286,19 @@
         <v>11</v>
       </c>
       <c r="E368" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="F368" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="G368" t="s">
         <v>25</v>
       </c>
       <c r="H368">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="I368">
-        <v>85</v>
+        <v>76</v>
       </c>
       <c r="J368">
         <v>0</v>
@@ -12318,19 +12318,19 @@
         <v>11</v>
       </c>
       <c r="E369" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="F369" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="G369" t="s">
         <v>26</v>
       </c>
       <c r="H369">
-        <v>85</v>
+        <v>76</v>
       </c>
       <c r="I369">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="J369">
         <v>0</v>
@@ -12338,7 +12338,7 @@
     </row>
     <row r="370" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A370" s="1">
-        <v>45534</v>
+        <v>45532</v>
       </c>
       <c r="B370">
         <v>2024</v>
@@ -12350,19 +12350,19 @@
         <v>11</v>
       </c>
       <c r="E370" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="F370" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="G370" t="s">
         <v>25</v>
       </c>
       <c r="H370">
-        <v>100</v>
+        <v>81</v>
       </c>
       <c r="I370">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="J370">
         <v>0</v>
@@ -12370,7 +12370,7 @@
     </row>
     <row r="371" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A371" s="1">
-        <v>45534</v>
+        <v>45532</v>
       </c>
       <c r="B371">
         <v>2024</v>
@@ -12382,19 +12382,19 @@
         <v>11</v>
       </c>
       <c r="E371" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="F371" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="G371" t="s">
         <v>26</v>
       </c>
       <c r="H371">
+        <v>85</v>
+      </c>
+      <c r="I371">
         <v>81</v>
-      </c>
-      <c r="I371">
-        <v>100</v>
       </c>
       <c r="J371">
         <v>0</v>
@@ -12414,19 +12414,19 @@
         <v>11</v>
       </c>
       <c r="E372" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="F372" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="G372" t="s">
         <v>25</v>
       </c>
       <c r="H372">
-        <v>76</v>
+        <v>100</v>
       </c>
       <c r="I372">
-        <v>94</v>
+        <v>81</v>
       </c>
       <c r="J372">
         <v>0</v>
@@ -12446,19 +12446,19 @@
         <v>11</v>
       </c>
       <c r="E373" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="F373" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="G373" t="s">
         <v>26</v>
       </c>
       <c r="H373">
-        <v>94</v>
+        <v>81</v>
       </c>
       <c r="I373">
-        <v>76</v>
+        <v>100</v>
       </c>
       <c r="J373">
         <v>0</v>
@@ -12478,19 +12478,19 @@
         <v>11</v>
       </c>
       <c r="E374" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="F374" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="G374" t="s">
         <v>25</v>
       </c>
       <c r="H374">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="I374">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="J374">
         <v>0</v>
@@ -12510,19 +12510,19 @@
         <v>11</v>
       </c>
       <c r="E375" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="F375" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="G375" t="s">
         <v>26</v>
       </c>
       <c r="H375">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="I375">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="J375">
         <v>0</v>
@@ -12542,19 +12542,19 @@
         <v>11</v>
       </c>
       <c r="E376" t="s">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="F376" t="s">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="G376" t="s">
         <v>25</v>
       </c>
       <c r="H376">
-        <v>98</v>
+        <v>72</v>
       </c>
       <c r="I376">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="J376">
         <v>0</v>
@@ -12574,19 +12574,19 @@
         <v>11</v>
       </c>
       <c r="E377" t="s">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="F377" t="s">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="G377" t="s">
         <v>26</v>
       </c>
       <c r="H377">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="I377">
-        <v>98</v>
+        <v>72</v>
       </c>
       <c r="J377">
         <v>0</v>
@@ -12594,7 +12594,7 @@
     </row>
     <row r="378" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A378" s="1">
-        <v>45535</v>
+        <v>45534</v>
       </c>
       <c r="B378">
         <v>2024</v>
@@ -12606,16 +12606,16 @@
         <v>11</v>
       </c>
       <c r="E378" t="s">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="F378" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="G378" t="s">
         <v>25</v>
       </c>
       <c r="H378">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="I378">
         <v>85</v>
@@ -12626,7 +12626,7 @@
     </row>
     <row r="379" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A379" s="1">
-        <v>45535</v>
+        <v>45534</v>
       </c>
       <c r="B379">
         <v>2024</v>
@@ -12638,10 +12638,10 @@
         <v>11</v>
       </c>
       <c r="E379" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="F379" t="s">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="G379" t="s">
         <v>26</v>
@@ -12650,7 +12650,7 @@
         <v>85</v>
       </c>
       <c r="I379">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="J379">
         <v>0</v>
@@ -12658,7 +12658,7 @@
     </row>
     <row r="380" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A380" s="1">
-        <v>45536</v>
+        <v>45535</v>
       </c>
       <c r="B380">
         <v>2024</v>
@@ -12670,19 +12670,19 @@
         <v>11</v>
       </c>
       <c r="E380" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="F380" t="s">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="G380" t="s">
         <v>25</v>
       </c>
       <c r="H380">
-        <v>86</v>
+        <v>96</v>
       </c>
       <c r="I380">
-        <v>93</v>
+        <v>85</v>
       </c>
       <c r="J380">
         <v>0</v>
@@ -12690,7 +12690,7 @@
     </row>
     <row r="381" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A381" s="1">
-        <v>45536</v>
+        <v>45535</v>
       </c>
       <c r="B381">
         <v>2024</v>
@@ -12702,19 +12702,19 @@
         <v>11</v>
       </c>
       <c r="E381" t="s">
+        <v>12</v>
+      </c>
+      <c r="F381" t="s">
         <v>19</v>
       </c>
-      <c r="F381" t="s">
-        <v>17</v>
-      </c>
       <c r="G381" t="s">
         <v>26</v>
       </c>
       <c r="H381">
-        <v>93</v>
+        <v>85</v>
       </c>
       <c r="I381">
-        <v>86</v>
+        <v>96</v>
       </c>
       <c r="J381">
         <v>0</v>
@@ -12734,16 +12734,16 @@
         <v>11</v>
       </c>
       <c r="E382" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F382" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="G382" t="s">
         <v>25</v>
       </c>
       <c r="H382">
-        <v>100</v>
+        <v>86</v>
       </c>
       <c r="I382">
         <v>93</v>
@@ -12766,10 +12766,10 @@
         <v>11</v>
       </c>
       <c r="E383" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="F383" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="G383" t="s">
         <v>26</v>
@@ -12778,7 +12778,7 @@
         <v>93</v>
       </c>
       <c r="I383">
-        <v>100</v>
+        <v>86</v>
       </c>
       <c r="J383">
         <v>0</v>
@@ -12798,19 +12798,19 @@
         <v>11</v>
       </c>
       <c r="E384" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="F384" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="G384" t="s">
         <v>25</v>
       </c>
       <c r="H384">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="I384">
-        <v>62</v>
+        <v>93</v>
       </c>
       <c r="J384">
         <v>0</v>
@@ -12830,19 +12830,19 @@
         <v>11</v>
       </c>
       <c r="E385" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="F385" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="G385" t="s">
         <v>26</v>
       </c>
       <c r="H385">
-        <v>62</v>
+        <v>93</v>
       </c>
       <c r="I385">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="J385">
         <v>0</v>
@@ -12862,19 +12862,19 @@
         <v>11</v>
       </c>
       <c r="E386" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F386" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G386" t="s">
         <v>25</v>
       </c>
       <c r="H386">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="I386">
-        <v>79</v>
+        <v>62</v>
       </c>
       <c r="J386">
         <v>0</v>
@@ -12894,19 +12894,19 @@
         <v>11</v>
       </c>
       <c r="E387" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="F387" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="G387" t="s">
         <v>26</v>
       </c>
       <c r="H387">
-        <v>79</v>
+        <v>62</v>
       </c>
       <c r="I387">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="J387">
         <v>0</v>
@@ -12926,16 +12926,16 @@
         <v>11</v>
       </c>
       <c r="E388" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="F388" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="G388" t="s">
         <v>25</v>
       </c>
       <c r="H388">
-        <v>97</v>
+        <v>74</v>
       </c>
       <c r="I388">
         <v>79</v>
@@ -12958,10 +12958,10 @@
         <v>11</v>
       </c>
       <c r="E389" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="F389" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="G389" t="s">
         <v>26</v>
@@ -12970,7 +12970,7 @@
         <v>79</v>
       </c>
       <c r="I389">
-        <v>97</v>
+        <v>74</v>
       </c>
       <c r="J389">
         <v>0</v>
@@ -12978,7 +12978,7 @@
     </row>
     <row r="390" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A390" s="1">
-        <v>45538</v>
+        <v>45536</v>
       </c>
       <c r="B390">
         <v>2024</v>
@@ -12990,19 +12990,19 @@
         <v>11</v>
       </c>
       <c r="E390" t="s">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="F390" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="G390" t="s">
         <v>25</v>
       </c>
       <c r="H390">
-        <v>71</v>
+        <v>97</v>
       </c>
       <c r="I390">
-        <v>64</v>
+        <v>79</v>
       </c>
       <c r="J390">
         <v>0</v>
@@ -13010,7 +13010,7 @@
     </row>
     <row r="391" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A391" s="1">
-        <v>45538</v>
+        <v>45536</v>
       </c>
       <c r="B391">
         <v>2024</v>
@@ -13022,19 +13022,19 @@
         <v>11</v>
       </c>
       <c r="E391" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="F391" t="s">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="G391" t="s">
         <v>26</v>
       </c>
       <c r="H391">
-        <v>64</v>
+        <v>79</v>
       </c>
       <c r="I391">
-        <v>71</v>
+        <v>97</v>
       </c>
       <c r="J391">
         <v>0</v>
@@ -13054,19 +13054,19 @@
         <v>11</v>
       </c>
       <c r="E392" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="F392" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="G392" t="s">
         <v>25</v>
       </c>
       <c r="H392">
-        <v>90</v>
+        <v>71</v>
       </c>
       <c r="I392">
-        <v>86</v>
+        <v>64</v>
       </c>
       <c r="J392">
         <v>0</v>
@@ -13086,19 +13086,19 @@
         <v>11</v>
       </c>
       <c r="E393" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="F393" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="G393" t="s">
         <v>26</v>
       </c>
       <c r="H393">
-        <v>86</v>
+        <v>64</v>
       </c>
       <c r="I393">
-        <v>90</v>
+        <v>71</v>
       </c>
       <c r="J393">
         <v>0</v>
@@ -13118,19 +13118,19 @@
         <v>11</v>
       </c>
       <c r="E394" t="s">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="F394" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="G394" t="s">
         <v>25</v>
       </c>
       <c r="H394">
-        <v>71</v>
+        <v>90</v>
       </c>
       <c r="I394">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="J394">
         <v>0</v>
@@ -13150,19 +13150,19 @@
         <v>11</v>
       </c>
       <c r="E395" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="F395" t="s">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="G395" t="s">
         <v>26</v>
       </c>
       <c r="H395">
+        <v>86</v>
+      </c>
+      <c r="I395">
         <v>90</v>
-      </c>
-      <c r="I395">
-        <v>71</v>
       </c>
       <c r="J395">
         <v>0</v>
@@ -13182,19 +13182,19 @@
         <v>11</v>
       </c>
       <c r="E396" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F396" t="s">
-        <v>14</v>
+        <v>24</v>
       </c>
       <c r="G396" t="s">
         <v>25</v>
       </c>
       <c r="H396">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="I396">
-        <v>74</v>
+        <v>90</v>
       </c>
       <c r="J396">
         <v>0</v>
@@ -13214,19 +13214,19 @@
         <v>11</v>
       </c>
       <c r="E397" t="s">
-        <v>14</v>
+        <v>24</v>
       </c>
       <c r="F397" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="G397" t="s">
         <v>26</v>
       </c>
       <c r="H397">
-        <v>74</v>
+        <v>90</v>
       </c>
       <c r="I397">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="J397">
         <v>0</v>
@@ -13234,7 +13234,7 @@
     </row>
     <row r="398" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A398" s="1">
-        <v>45539</v>
+        <v>45538</v>
       </c>
       <c r="B398">
         <v>2024</v>
@@ -13246,19 +13246,19 @@
         <v>11</v>
       </c>
       <c r="E398" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="F398" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="G398" t="s">
         <v>25</v>
       </c>
       <c r="H398">
-        <v>86</v>
+        <v>66</v>
       </c>
       <c r="I398">
-        <v>93</v>
+        <v>74</v>
       </c>
       <c r="J398">
         <v>0</v>
@@ -13266,7 +13266,7 @@
     </row>
     <row r="399" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A399" s="1">
-        <v>45539</v>
+        <v>45538</v>
       </c>
       <c r="B399">
         <v>2024</v>
@@ -13278,19 +13278,19 @@
         <v>11</v>
       </c>
       <c r="E399" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="F399" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="G399" t="s">
         <v>26</v>
       </c>
       <c r="H399">
-        <v>93</v>
+        <v>74</v>
       </c>
       <c r="I399">
-        <v>86</v>
+        <v>66</v>
       </c>
       <c r="J399">
         <v>0</v>
@@ -13298,7 +13298,7 @@
     </row>
     <row r="400" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A400" s="1">
-        <v>45540</v>
+        <v>45539</v>
       </c>
       <c r="B400">
         <v>2024</v>
@@ -13310,19 +13310,19 @@
         <v>11</v>
       </c>
       <c r="E400" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F400" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="G400" t="s">
         <v>25</v>
       </c>
       <c r="H400">
-        <v>70</v>
+        <v>86</v>
       </c>
       <c r="I400">
-        <v>77</v>
+        <v>93</v>
       </c>
       <c r="J400">
         <v>0</v>
@@ -13330,7 +13330,7 @@
     </row>
     <row r="401" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A401" s="1">
-        <v>45540</v>
+        <v>45539</v>
       </c>
       <c r="B401">
         <v>2024</v>
@@ -13342,19 +13342,19 @@
         <v>11</v>
       </c>
       <c r="E401" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="F401" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="G401" t="s">
         <v>26</v>
       </c>
       <c r="H401">
-        <v>77</v>
+        <v>93</v>
       </c>
       <c r="I401">
-        <v>70</v>
+        <v>86</v>
       </c>
       <c r="J401">
         <v>0</v>
@@ -13374,16 +13374,16 @@
         <v>11</v>
       </c>
       <c r="E402" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="F402" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G402" t="s">
         <v>25</v>
       </c>
       <c r="H402">
-        <v>90</v>
+        <v>70</v>
       </c>
       <c r="I402">
         <v>77</v>
@@ -13406,10 +13406,10 @@
         <v>11</v>
       </c>
       <c r="E403" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F403" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="G403" t="s">
         <v>26</v>
@@ -13418,7 +13418,7 @@
         <v>77</v>
       </c>
       <c r="I403">
-        <v>90</v>
+        <v>70</v>
       </c>
       <c r="J403">
         <v>0</v>
@@ -13426,7 +13426,7 @@
     </row>
     <row r="404" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A404" s="1">
-        <v>45541</v>
+        <v>45540</v>
       </c>
       <c r="B404">
         <v>2024</v>
@@ -13438,27 +13438,27 @@
         <v>11</v>
       </c>
       <c r="E404" t="s">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="F404" t="s">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="G404" t="s">
         <v>25</v>
       </c>
       <c r="H404">
-        <v>96</v>
+        <v>90</v>
       </c>
       <c r="I404">
-        <v>107</v>
+        <v>77</v>
       </c>
       <c r="J404">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="405" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A405" s="1">
-        <v>45541</v>
+        <v>45540</v>
       </c>
       <c r="B405">
         <v>2024</v>
@@ -13470,22 +13470,22 @@
         <v>11</v>
       </c>
       <c r="E405" t="s">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="F405" t="s">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="G405" t="s">
         <v>26</v>
       </c>
       <c r="H405">
-        <v>107</v>
+        <v>77</v>
       </c>
       <c r="I405">
-        <v>96</v>
+        <v>90</v>
       </c>
       <c r="J405">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="406" spans="1:10" x14ac:dyDescent="0.35">
@@ -13502,22 +13502,22 @@
         <v>11</v>
       </c>
       <c r="E406" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="F406" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="G406" t="s">
         <v>25</v>
       </c>
       <c r="H406">
-        <v>78</v>
+        <v>96</v>
       </c>
       <c r="I406">
-        <v>92</v>
+        <v>107</v>
       </c>
       <c r="J406">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="407" spans="1:10" x14ac:dyDescent="0.35">
@@ -13534,22 +13534,22 @@
         <v>11</v>
       </c>
       <c r="E407" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F407" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="G407" t="s">
         <v>26</v>
       </c>
       <c r="H407">
-        <v>92</v>
+        <v>107</v>
       </c>
       <c r="I407">
-        <v>78</v>
+        <v>96</v>
       </c>
       <c r="J407">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="408" spans="1:10" x14ac:dyDescent="0.35">
@@ -13566,19 +13566,19 @@
         <v>11</v>
       </c>
       <c r="E408" t="s">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="F408" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G408" t="s">
         <v>25</v>
       </c>
       <c r="H408">
-        <v>72</v>
+        <v>78</v>
       </c>
       <c r="I408">
-        <v>67</v>
+        <v>92</v>
       </c>
       <c r="J408">
         <v>0</v>
@@ -13598,19 +13598,19 @@
         <v>11</v>
       </c>
       <c r="E409" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F409" t="s">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="G409" t="s">
         <v>26</v>
       </c>
       <c r="H409">
-        <v>67</v>
+        <v>92</v>
       </c>
       <c r="I409">
-        <v>72</v>
+        <v>78</v>
       </c>
       <c r="J409">
         <v>0</v>
@@ -13630,19 +13630,19 @@
         <v>11</v>
       </c>
       <c r="E410" t="s">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="F410" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G410" t="s">
         <v>25</v>
       </c>
       <c r="H410">
-        <v>99</v>
+        <v>72</v>
       </c>
       <c r="I410">
-        <v>88</v>
+        <v>67</v>
       </c>
       <c r="J410">
         <v>0</v>
@@ -13662,19 +13662,19 @@
         <v>11</v>
       </c>
       <c r="E411" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F411" t="s">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="G411" t="s">
         <v>26</v>
       </c>
       <c r="H411">
-        <v>88</v>
+        <v>67</v>
       </c>
       <c r="I411">
-        <v>99</v>
+        <v>72</v>
       </c>
       <c r="J411">
         <v>0</v>
@@ -13682,7 +13682,7 @@
     </row>
     <row r="412" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A412" s="1">
-        <v>45542</v>
+        <v>45541</v>
       </c>
       <c r="B412">
         <v>2024</v>
@@ -13694,19 +13694,19 @@
         <v>11</v>
       </c>
       <c r="E412" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="F412" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="G412" t="s">
         <v>25</v>
       </c>
       <c r="H412">
-        <v>66</v>
+        <v>99</v>
       </c>
       <c r="I412">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="J412">
         <v>0</v>
@@ -13714,7 +13714,7 @@
     </row>
     <row r="413" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A413" s="1">
-        <v>45542</v>
+        <v>45541</v>
       </c>
       <c r="B413">
         <v>2024</v>
@@ -13726,19 +13726,19 @@
         <v>11</v>
       </c>
       <c r="E413" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F413" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="G413" t="s">
         <v>26</v>
       </c>
       <c r="H413">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="I413">
-        <v>66</v>
+        <v>99</v>
       </c>
       <c r="J413">
         <v>0</v>
@@ -13746,7 +13746,7 @@
     </row>
     <row r="414" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A414" s="1">
-        <v>45543</v>
+        <v>45542</v>
       </c>
       <c r="B414">
         <v>2024</v>
@@ -13758,19 +13758,19 @@
         <v>11</v>
       </c>
       <c r="E414" t="s">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="F414" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="G414" t="s">
         <v>25</v>
       </c>
       <c r="H414">
-        <v>77</v>
+        <v>66</v>
       </c>
       <c r="I414">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="J414">
         <v>0</v>
@@ -13778,7 +13778,7 @@
     </row>
     <row r="415" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A415" s="1">
-        <v>45543</v>
+        <v>45542</v>
       </c>
       <c r="B415">
         <v>2024</v>
@@ -13790,19 +13790,19 @@
         <v>11</v>
       </c>
       <c r="E415" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="F415" t="s">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="G415" t="s">
         <v>26</v>
       </c>
       <c r="H415">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="I415">
-        <v>77</v>
+        <v>66</v>
       </c>
       <c r="J415">
         <v>0</v>
@@ -13822,22 +13822,22 @@
         <v>11</v>
       </c>
       <c r="E416" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F416" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="G416" t="s">
         <v>25</v>
       </c>
       <c r="H416">
-        <v>100</v>
+        <v>77</v>
       </c>
       <c r="I416">
-        <v>104</v>
+        <v>92</v>
       </c>
       <c r="J416">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="417" spans="1:10" x14ac:dyDescent="0.35">
@@ -13854,22 +13854,22 @@
         <v>11</v>
       </c>
       <c r="E417" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="F417" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="G417" t="s">
         <v>26</v>
       </c>
       <c r="H417">
-        <v>104</v>
+        <v>92</v>
       </c>
       <c r="I417">
-        <v>100</v>
+        <v>77</v>
       </c>
       <c r="J417">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="418" spans="1:10" x14ac:dyDescent="0.35">
@@ -13886,22 +13886,22 @@
         <v>11</v>
       </c>
       <c r="E418" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="F418" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="G418" t="s">
         <v>25</v>
       </c>
       <c r="H418">
-        <v>79</v>
+        <v>100</v>
       </c>
       <c r="I418">
-        <v>67</v>
+        <v>104</v>
       </c>
       <c r="J418">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="419" spans="1:10" x14ac:dyDescent="0.35">
@@ -13918,22 +13918,22 @@
         <v>11</v>
       </c>
       <c r="E419" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="F419" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="G419" t="s">
         <v>26</v>
       </c>
       <c r="H419">
-        <v>67</v>
+        <v>104</v>
       </c>
       <c r="I419">
-        <v>79</v>
+        <v>100</v>
       </c>
       <c r="J419">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="420" spans="1:10" x14ac:dyDescent="0.35">
@@ -13950,19 +13950,19 @@
         <v>11</v>
       </c>
       <c r="E420" t="s">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="F420" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="G420" t="s">
         <v>25</v>
       </c>
       <c r="H420">
-        <v>71</v>
+        <v>79</v>
       </c>
       <c r="I420">
-        <v>75</v>
+        <v>67</v>
       </c>
       <c r="J420">
         <v>0</v>
@@ -13982,19 +13982,19 @@
         <v>11</v>
       </c>
       <c r="E421" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="F421" t="s">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="G421" t="s">
         <v>26</v>
       </c>
       <c r="H421">
-        <v>75</v>
+        <v>67</v>
       </c>
       <c r="I421">
-        <v>71</v>
+        <v>79</v>
       </c>
       <c r="J421">
         <v>0</v>
@@ -14014,19 +14014,19 @@
         <v>11</v>
       </c>
       <c r="E422" t="s">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="F422" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G422" t="s">
         <v>25</v>
       </c>
       <c r="H422">
-        <v>78</v>
+        <v>71</v>
       </c>
       <c r="I422">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="J422">
         <v>0</v>
@@ -14046,19 +14046,19 @@
         <v>11</v>
       </c>
       <c r="E423" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F423" t="s">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="G423" t="s">
         <v>26</v>
       </c>
       <c r="H423">
+        <v>75</v>
+      </c>
+      <c r="I423">
         <v>71</v>
-      </c>
-      <c r="I423">
-        <v>78</v>
       </c>
       <c r="J423">
         <v>0</v>
@@ -14066,7 +14066,7 @@
     </row>
     <row r="424" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A424" s="1">
-        <v>45545</v>
+        <v>45543</v>
       </c>
       <c r="B424">
         <v>2024</v>
@@ -14081,16 +14081,16 @@
         <v>16</v>
       </c>
       <c r="F424" t="s">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="G424" t="s">
         <v>25</v>
       </c>
       <c r="H424">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="I424">
-        <v>64</v>
+        <v>71</v>
       </c>
       <c r="J424">
         <v>0</v>
@@ -14098,7 +14098,7 @@
     </row>
     <row r="425" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A425" s="1">
-        <v>45545</v>
+        <v>45543</v>
       </c>
       <c r="B425">
         <v>2024</v>
@@ -14110,7 +14110,7 @@
         <v>11</v>
       </c>
       <c r="E425" t="s">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="F425" t="s">
         <v>16</v>
@@ -14119,10 +14119,10 @@
         <v>26</v>
       </c>
       <c r="H425">
-        <v>64</v>
+        <v>71</v>
       </c>
       <c r="I425">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="J425">
         <v>0</v>
@@ -14142,19 +14142,19 @@
         <v>11</v>
       </c>
       <c r="E426" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="F426" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="G426" t="s">
         <v>25</v>
       </c>
       <c r="H426">
-        <v>105</v>
+        <v>76</v>
       </c>
       <c r="I426">
-        <v>91</v>
+        <v>64</v>
       </c>
       <c r="J426">
         <v>0</v>
@@ -14174,19 +14174,19 @@
         <v>11</v>
       </c>
       <c r="E427" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F427" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="G427" t="s">
         <v>26</v>
       </c>
       <c r="H427">
-        <v>91</v>
+        <v>64</v>
       </c>
       <c r="I427">
-        <v>105</v>
+        <v>76</v>
       </c>
       <c r="J427">
         <v>0</v>
@@ -14206,19 +14206,19 @@
         <v>11</v>
       </c>
       <c r="E428" t="s">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="F428" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="G428" t="s">
         <v>25</v>
       </c>
       <c r="H428">
-        <v>86</v>
+        <v>105</v>
       </c>
       <c r="I428">
-        <v>66</v>
+        <v>91</v>
       </c>
       <c r="J428">
         <v>0</v>
@@ -14238,19 +14238,19 @@
         <v>11</v>
       </c>
       <c r="E429" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="F429" t="s">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="G429" t="s">
         <v>26</v>
       </c>
       <c r="H429">
-        <v>66</v>
+        <v>91</v>
       </c>
       <c r="I429">
-        <v>86</v>
+        <v>105</v>
       </c>
       <c r="J429">
         <v>0</v>
@@ -14258,7 +14258,7 @@
     </row>
     <row r="430" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A430" s="1">
-        <v>45546</v>
+        <v>45545</v>
       </c>
       <c r="B430">
         <v>2024</v>
@@ -14270,19 +14270,19 @@
         <v>11</v>
       </c>
       <c r="E430" t="s">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="F430" t="s">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="G430" t="s">
         <v>25</v>
       </c>
       <c r="H430">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="I430">
-        <v>58</v>
+        <v>66</v>
       </c>
       <c r="J430">
         <v>0</v>
@@ -14290,7 +14290,7 @@
     </row>
     <row r="431" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A431" s="1">
-        <v>45546</v>
+        <v>45545</v>
       </c>
       <c r="B431">
         <v>2024</v>
@@ -14302,19 +14302,19 @@
         <v>11</v>
       </c>
       <c r="E431" t="s">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="F431" t="s">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="G431" t="s">
         <v>26</v>
       </c>
       <c r="H431">
-        <v>58</v>
+        <v>66</v>
       </c>
       <c r="I431">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="J431">
         <v>0</v>
@@ -14334,19 +14334,19 @@
         <v>11</v>
       </c>
       <c r="E432" t="s">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="F432" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="G432" t="s">
         <v>25</v>
       </c>
       <c r="H432">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="I432">
-        <v>75</v>
+        <v>58</v>
       </c>
       <c r="J432">
         <v>0</v>
@@ -14366,19 +14366,19 @@
         <v>11</v>
       </c>
       <c r="E433" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="F433" t="s">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="G433" t="s">
         <v>26</v>
       </c>
       <c r="H433">
-        <v>75</v>
+        <v>58</v>
       </c>
       <c r="I433">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="J433">
         <v>0</v>
@@ -14398,19 +14398,19 @@
         <v>11</v>
       </c>
       <c r="E434" t="s">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="F434" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="G434" t="s">
         <v>25</v>
       </c>
       <c r="H434">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="I434">
-        <v>82</v>
+        <v>75</v>
       </c>
       <c r="J434">
         <v>0</v>
@@ -14430,19 +14430,19 @@
         <v>11</v>
       </c>
       <c r="E435" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="F435" t="s">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="G435" t="s">
         <v>26</v>
       </c>
       <c r="H435">
-        <v>82</v>
+        <v>75</v>
       </c>
       <c r="I435">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="J435">
         <v>0</v>
@@ -14450,7 +14450,7 @@
     </row>
     <row r="436" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A436" s="1">
-        <v>45547</v>
+        <v>45546</v>
       </c>
       <c r="B436">
         <v>2024</v>
@@ -14462,19 +14462,19 @@
         <v>11</v>
       </c>
       <c r="E436" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="F436" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="G436" t="s">
         <v>25</v>
       </c>
       <c r="H436">
-        <v>99</v>
+        <v>90</v>
       </c>
       <c r="I436">
-        <v>67</v>
+        <v>82</v>
       </c>
       <c r="J436">
         <v>0</v>
@@ -14482,7 +14482,7 @@
     </row>
     <row r="437" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A437" s="1">
-        <v>45547</v>
+        <v>45546</v>
       </c>
       <c r="B437">
         <v>2024</v>
@@ -14494,19 +14494,19 @@
         <v>11</v>
       </c>
       <c r="E437" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="F437" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="G437" t="s">
         <v>26</v>
       </c>
       <c r="H437">
-        <v>67</v>
+        <v>82</v>
       </c>
       <c r="I437">
-        <v>99</v>
+        <v>90</v>
       </c>
       <c r="J437">
         <v>0</v>
@@ -14514,7 +14514,7 @@
     </row>
     <row r="438" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A438" s="1">
-        <v>45548</v>
+        <v>45547</v>
       </c>
       <c r="B438">
         <v>2024</v>
@@ -14526,19 +14526,19 @@
         <v>11</v>
       </c>
       <c r="E438" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F438" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="G438" t="s">
         <v>25</v>
       </c>
       <c r="H438">
-        <v>72</v>
+        <v>99</v>
       </c>
       <c r="I438">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="J438">
         <v>0</v>
@@ -14546,7 +14546,7 @@
     </row>
     <row r="439" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A439" s="1">
-        <v>45548</v>
+        <v>45547</v>
       </c>
       <c r="B439">
         <v>2024</v>
@@ -14558,19 +14558,19 @@
         <v>11</v>
       </c>
       <c r="E439" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F439" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G439" t="s">
         <v>26</v>
       </c>
       <c r="H439">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="I439">
-        <v>72</v>
+        <v>99</v>
       </c>
       <c r="J439">
         <v>0</v>
@@ -14590,19 +14590,19 @@
         <v>11</v>
       </c>
       <c r="E440" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="F440" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="G440" t="s">
         <v>25</v>
       </c>
       <c r="H440">
-        <v>83</v>
+        <v>72</v>
       </c>
       <c r="I440">
-        <v>81</v>
+        <v>69</v>
       </c>
       <c r="J440">
         <v>0</v>
@@ -14622,19 +14622,19 @@
         <v>11</v>
       </c>
       <c r="E441" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F441" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="G441" t="s">
         <v>26</v>
       </c>
       <c r="H441">
-        <v>81</v>
+        <v>69</v>
       </c>
       <c r="I441">
-        <v>83</v>
+        <v>72</v>
       </c>
       <c r="J441">
         <v>0</v>
@@ -14654,19 +14654,19 @@
         <v>11</v>
       </c>
       <c r="E442" t="s">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="F442" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="G442" t="s">
         <v>25</v>
       </c>
       <c r="H442">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="I442">
-        <v>74</v>
+        <v>81</v>
       </c>
       <c r="J442">
         <v>0</v>
@@ -14686,19 +14686,19 @@
         <v>11</v>
       </c>
       <c r="E443" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="F443" t="s">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="G443" t="s">
         <v>26</v>
       </c>
       <c r="H443">
-        <v>74</v>
+        <v>81</v>
       </c>
       <c r="I443">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="J443">
         <v>0</v>
@@ -14718,19 +14718,19 @@
         <v>11</v>
       </c>
       <c r="E444" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="F444" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="G444" t="s">
         <v>25</v>
       </c>
       <c r="H444">
-        <v>66</v>
+        <v>78</v>
       </c>
       <c r="I444">
-        <v>83</v>
+        <v>74</v>
       </c>
       <c r="J444">
         <v>0</v>
@@ -14750,19 +14750,19 @@
         <v>11</v>
       </c>
       <c r="E445" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="F445" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="G445" t="s">
         <v>26</v>
       </c>
       <c r="H445">
-        <v>83</v>
+        <v>74</v>
       </c>
       <c r="I445">
-        <v>66</v>
+        <v>78</v>
       </c>
       <c r="J445">
         <v>0</v>
@@ -14782,19 +14782,19 @@
         <v>11</v>
       </c>
       <c r="E446" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F446" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="G446" t="s">
         <v>25</v>
       </c>
       <c r="H446">
-        <v>88</v>
+        <v>66</v>
       </c>
       <c r="I446">
-        <v>69</v>
+        <v>83</v>
       </c>
       <c r="J446">
         <v>0</v>
@@ -14814,19 +14814,19 @@
         <v>11</v>
       </c>
       <c r="E447" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="F447" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G447" t="s">
         <v>26</v>
       </c>
       <c r="H447">
-        <v>69</v>
+        <v>83</v>
       </c>
       <c r="I447">
-        <v>88</v>
+        <v>66</v>
       </c>
       <c r="J447">
         <v>0</v>
@@ -14834,7 +14834,7 @@
     </row>
     <row r="448" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A448" s="1">
-        <v>45550</v>
+        <v>45548</v>
       </c>
       <c r="B448">
         <v>2024</v>
@@ -14846,19 +14846,19 @@
         <v>11</v>
       </c>
       <c r="E448" t="s">
+        <v>19</v>
+      </c>
+      <c r="F448" t="s">
         <v>14</v>
       </c>
-      <c r="F448" t="s">
-        <v>20</v>
-      </c>
       <c r="G448" t="s">
         <v>25</v>
       </c>
       <c r="H448">
-        <v>93</v>
+        <v>88</v>
       </c>
       <c r="I448">
-        <v>88</v>
+        <v>69</v>
       </c>
       <c r="J448">
         <v>0</v>
@@ -14866,7 +14866,7 @@
     </row>
     <row r="449" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A449" s="1">
-        <v>45550</v>
+        <v>45548</v>
       </c>
       <c r="B449">
         <v>2024</v>
@@ -14878,19 +14878,19 @@
         <v>11</v>
       </c>
       <c r="E449" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="F449" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="G449" t="s">
         <v>26</v>
       </c>
       <c r="H449">
+        <v>69</v>
+      </c>
+      <c r="I449">
         <v>88</v>
-      </c>
-      <c r="I449">
-        <v>93</v>
       </c>
       <c r="J449">
         <v>0</v>
@@ -14910,19 +14910,19 @@
         <v>11</v>
       </c>
       <c r="E450" t="s">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="F450" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="G450" t="s">
         <v>25</v>
       </c>
       <c r="H450">
-        <v>109</v>
+        <v>93</v>
       </c>
       <c r="I450">
-        <v>110</v>
+        <v>88</v>
       </c>
       <c r="J450">
         <v>0</v>
@@ -14942,19 +14942,19 @@
         <v>11</v>
       </c>
       <c r="E451" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="F451" t="s">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="G451" t="s">
         <v>26</v>
       </c>
       <c r="H451">
-        <v>110</v>
+        <v>88</v>
       </c>
       <c r="I451">
-        <v>109</v>
+        <v>93</v>
       </c>
       <c r="J451">
         <v>0</v>
@@ -14974,19 +14974,19 @@
         <v>11</v>
       </c>
       <c r="E452" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="F452" t="s">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="G452" t="s">
         <v>25</v>
       </c>
       <c r="H452">
-        <v>71</v>
+        <v>109</v>
       </c>
       <c r="I452">
-        <v>84</v>
+        <v>110</v>
       </c>
       <c r="J452">
         <v>0</v>
@@ -15006,19 +15006,19 @@
         <v>11</v>
       </c>
       <c r="E453" t="s">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="F453" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="G453" t="s">
         <v>26</v>
       </c>
       <c r="H453">
-        <v>84</v>
+        <v>110</v>
       </c>
       <c r="I453">
-        <v>71</v>
+        <v>109</v>
       </c>
       <c r="J453">
         <v>0</v>
@@ -15038,19 +15038,19 @@
         <v>11</v>
       </c>
       <c r="E454" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="F454" t="s">
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="G454" t="s">
         <v>25</v>
       </c>
       <c r="H454">
-        <v>88</v>
+        <v>71</v>
       </c>
       <c r="I454">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="J454">
         <v>0</v>
@@ -15070,19 +15070,19 @@
         <v>11</v>
       </c>
       <c r="E455" t="s">
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="F455" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="G455" t="s">
         <v>26</v>
       </c>
       <c r="H455">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="I455">
-        <v>88</v>
+        <v>71</v>
       </c>
       <c r="J455">
         <v>0</v>
@@ -15102,19 +15102,19 @@
         <v>11</v>
       </c>
       <c r="E456" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F456" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="G456" t="s">
         <v>25</v>
       </c>
       <c r="H456">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="I456">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="J456">
         <v>0</v>
@@ -15134,19 +15134,19 @@
         <v>11</v>
       </c>
       <c r="E457" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="F457" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G457" t="s">
         <v>26</v>
       </c>
       <c r="H457">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="I457">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="J457">
         <v>0</v>
@@ -15166,22 +15166,22 @@
         <v>11</v>
       </c>
       <c r="E458" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="F458" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="G458" t="s">
         <v>25</v>
       </c>
       <c r="H458">
-        <v>76</v>
+        <v>87</v>
       </c>
       <c r="I458">
-        <v>73</v>
+        <v>90</v>
       </c>
       <c r="J458">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="459" spans="1:10" x14ac:dyDescent="0.35">
@@ -15198,27 +15198,27 @@
         <v>11</v>
       </c>
       <c r="E459" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="F459" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="G459" t="s">
         <v>26</v>
       </c>
       <c r="H459">
-        <v>73</v>
+        <v>90</v>
       </c>
       <c r="I459">
-        <v>76</v>
+        <v>87</v>
       </c>
       <c r="J459">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="460" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A460" s="1">
-        <v>45552</v>
+        <v>45550</v>
       </c>
       <c r="B460">
         <v>2024</v>
@@ -15230,27 +15230,27 @@
         <v>11</v>
       </c>
       <c r="E460" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F460" t="s">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="G460" t="s">
         <v>25</v>
       </c>
       <c r="H460">
-        <v>70</v>
+        <v>76</v>
       </c>
       <c r="I460">
-        <v>86</v>
+        <v>73</v>
       </c>
       <c r="J460">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="461" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A461" s="1">
-        <v>45552</v>
+        <v>45550</v>
       </c>
       <c r="B461">
         <v>2024</v>
@@ -15262,22 +15262,22 @@
         <v>11</v>
       </c>
       <c r="E461" t="s">
+        <v>12</v>
+      </c>
+      <c r="F461" t="s">
         <v>21</v>
       </c>
-      <c r="F461" t="s">
-        <v>20</v>
-      </c>
       <c r="G461" t="s">
         <v>26</v>
       </c>
       <c r="H461">
-        <v>86</v>
+        <v>73</v>
       </c>
       <c r="I461">
-        <v>70</v>
+        <v>76</v>
       </c>
       <c r="J461">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="462" spans="1:10" x14ac:dyDescent="0.35">
@@ -15294,19 +15294,19 @@
         <v>11</v>
       </c>
       <c r="E462" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="F462" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="G462" t="s">
         <v>25</v>
       </c>
       <c r="H462">
-        <v>78</v>
+        <v>70</v>
       </c>
       <c r="I462">
-        <v>76</v>
+        <v>86</v>
       </c>
       <c r="J462">
         <v>0</v>
@@ -15326,19 +15326,19 @@
         <v>11</v>
       </c>
       <c r="E463" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="F463" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="G463" t="s">
         <v>26</v>
       </c>
       <c r="H463">
-        <v>76</v>
+        <v>86</v>
       </c>
       <c r="I463">
-        <v>78</v>
+        <v>70</v>
       </c>
       <c r="J463">
         <v>0</v>
@@ -15358,19 +15358,19 @@
         <v>11</v>
       </c>
       <c r="E464" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="F464" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="G464" t="s">
         <v>25</v>
       </c>
       <c r="H464">
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="I464">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="J464">
         <v>0</v>
@@ -15390,19 +15390,19 @@
         <v>11</v>
       </c>
       <c r="E465" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="F465" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="G465" t="s">
         <v>26</v>
       </c>
       <c r="H465">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="I465">
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="J465">
         <v>0</v>
@@ -15422,10 +15422,10 @@
         <v>11</v>
       </c>
       <c r="E466" t="s">
-        <v>24</v>
+        <v>14</v>
       </c>
       <c r="F466" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="G466" t="s">
         <v>25</v>
@@ -15434,7 +15434,7 @@
         <v>85</v>
       </c>
       <c r="I466">
-        <v>72</v>
+        <v>81</v>
       </c>
       <c r="J466">
         <v>0</v>
@@ -15454,16 +15454,16 @@
         <v>11</v>
       </c>
       <c r="E467" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F467" t="s">
-        <v>24</v>
+        <v>14</v>
       </c>
       <c r="G467" t="s">
         <v>26</v>
       </c>
       <c r="H467">
-        <v>72</v>
+        <v>81</v>
       </c>
       <c r="I467">
         <v>85</v>
@@ -15486,19 +15486,19 @@
         <v>11</v>
       </c>
       <c r="E468" t="s">
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="F468" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="G468" t="s">
         <v>25</v>
       </c>
       <c r="H468">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="I468">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="J468">
         <v>0</v>
@@ -15518,19 +15518,19 @@
         <v>11</v>
       </c>
       <c r="E469" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="F469" t="s">
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="G469" t="s">
         <v>26</v>
       </c>
       <c r="H469">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="I469">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="J469">
         <v>0</v>
@@ -15538,7 +15538,7 @@
     </row>
     <row r="470" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A470" s="1">
-        <v>45554</v>
+        <v>45552</v>
       </c>
       <c r="B470">
         <v>2024</v>
@@ -15550,19 +15550,19 @@
         <v>11</v>
       </c>
       <c r="E470" t="s">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="F470" t="s">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="G470" t="s">
         <v>25</v>
       </c>
       <c r="H470">
-        <v>54</v>
+        <v>87</v>
       </c>
       <c r="I470">
-        <v>87</v>
+        <v>71</v>
       </c>
       <c r="J470">
         <v>0</v>
@@ -15570,7 +15570,7 @@
     </row>
     <row r="471" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A471" s="1">
-        <v>45554</v>
+        <v>45552</v>
       </c>
       <c r="B471">
         <v>2024</v>
@@ -15582,19 +15582,19 @@
         <v>11</v>
       </c>
       <c r="E471" t="s">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="F471" t="s">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="G471" t="s">
         <v>26</v>
       </c>
       <c r="H471">
+        <v>71</v>
+      </c>
+      <c r="I471">
         <v>87</v>
-      </c>
-      <c r="I471">
-        <v>54</v>
       </c>
       <c r="J471">
         <v>0</v>
@@ -15614,19 +15614,19 @@
         <v>11</v>
       </c>
       <c r="E472" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="F472" t="s">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="G472" t="s">
         <v>25</v>
       </c>
       <c r="H472">
-        <v>84</v>
+        <v>54</v>
       </c>
       <c r="I472">
-        <v>98</v>
+        <v>87</v>
       </c>
       <c r="J472">
         <v>0</v>
@@ -15646,19 +15646,19 @@
         <v>11</v>
       </c>
       <c r="E473" t="s">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="F473" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="G473" t="s">
         <v>26</v>
       </c>
       <c r="H473">
-        <v>98</v>
+        <v>87</v>
       </c>
       <c r="I473">
-        <v>84</v>
+        <v>54</v>
       </c>
       <c r="J473">
         <v>0</v>
@@ -15678,19 +15678,19 @@
         <v>11</v>
       </c>
       <c r="E474" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="F474" t="s">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="G474" t="s">
         <v>25</v>
       </c>
       <c r="H474">
-        <v>68</v>
+        <v>84</v>
       </c>
       <c r="I474">
-        <v>51</v>
+        <v>98</v>
       </c>
       <c r="J474">
         <v>0</v>
@@ -15710,19 +15710,19 @@
         <v>11</v>
       </c>
       <c r="E475" t="s">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="F475" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="G475" t="s">
         <v>26</v>
       </c>
       <c r="H475">
-        <v>51</v>
+        <v>98</v>
       </c>
       <c r="I475">
-        <v>68</v>
+        <v>84</v>
       </c>
       <c r="J475">
         <v>0</v>
@@ -15742,19 +15742,19 @@
         <v>11</v>
       </c>
       <c r="E476" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="F476" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="G476" t="s">
         <v>25</v>
       </c>
       <c r="H476">
-        <v>78</v>
+        <v>68</v>
       </c>
       <c r="I476">
-        <v>67</v>
+        <v>51</v>
       </c>
       <c r="J476">
         <v>0</v>
@@ -15774,19 +15774,19 @@
         <v>11</v>
       </c>
       <c r="E477" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="F477" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="G477" t="s">
         <v>26</v>
       </c>
       <c r="H477">
-        <v>67</v>
+        <v>51</v>
       </c>
       <c r="I477">
-        <v>78</v>
+        <v>68</v>
       </c>
       <c r="J477">
         <v>0</v>
@@ -15806,19 +15806,19 @@
         <v>11</v>
       </c>
       <c r="E478" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="F478" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G478" t="s">
         <v>25</v>
       </c>
       <c r="H478">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="I478">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="J478">
         <v>0</v>
@@ -15838,19 +15838,19 @@
         <v>11</v>
       </c>
       <c r="E479" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F479" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="G479" t="s">
         <v>26</v>
       </c>
       <c r="H479">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="I479">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="J479">
         <v>0</v>
@@ -15870,19 +15870,19 @@
         <v>11</v>
       </c>
       <c r="E480" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F480" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="G480" t="s">
         <v>25</v>
       </c>
       <c r="H480">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="I480">
-        <v>92</v>
+        <v>70</v>
       </c>
       <c r="J480">
         <v>0</v>
@@ -15902,19 +15902,19 @@
         <v>11</v>
       </c>
       <c r="E481" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="F481" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="G481" t="s">
         <v>26</v>
       </c>
       <c r="H481">
-        <v>92</v>
+        <v>70</v>
       </c>
       <c r="I481">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="J481">
         <v>0</v>
@@ -15922,31 +15922,31 @@
     </row>
     <row r="482" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A482" s="1">
-        <v>45557</v>
+        <v>45554</v>
       </c>
       <c r="B482">
         <v>2024</v>
       </c>
       <c r="C482" t="s">
-        <v>23</v>
-      </c>
-      <c r="D482">
-        <v>1</v>
+        <v>10</v>
+      </c>
+      <c r="D482" t="s">
+        <v>11</v>
       </c>
       <c r="E482" t="s">
         <v>18</v>
       </c>
       <c r="F482" t="s">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="G482" t="s">
         <v>25</v>
       </c>
       <c r="H482">
-        <v>69</v>
+        <v>91</v>
       </c>
       <c r="I482">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="J482">
         <v>0</v>
@@ -15954,19 +15954,19 @@
     </row>
     <row r="483" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A483" s="1">
-        <v>45557</v>
+        <v>45554</v>
       </c>
       <c r="B483">
         <v>2024</v>
       </c>
       <c r="C483" t="s">
-        <v>23</v>
-      </c>
-      <c r="D483">
-        <v>1</v>
+        <v>10</v>
+      </c>
+      <c r="D483" t="s">
+        <v>11</v>
       </c>
       <c r="E483" t="s">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="F483" t="s">
         <v>18</v>
@@ -15975,10 +15975,10 @@
         <v>26</v>
       </c>
       <c r="H483">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="I483">
-        <v>69</v>
+        <v>91</v>
       </c>
       <c r="J483">
         <v>0</v>
@@ -15998,19 +15998,19 @@
         <v>1</v>
       </c>
       <c r="E484" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F484" t="s">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="G484" t="s">
         <v>25</v>
       </c>
       <c r="H484">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="I484">
-        <v>78</v>
+        <v>93</v>
       </c>
       <c r="J484">
         <v>0</v>
@@ -16030,19 +16030,19 @@
         <v>1</v>
       </c>
       <c r="E485" t="s">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="F485" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="G485" t="s">
         <v>26</v>
       </c>
       <c r="H485">
-        <v>78</v>
+        <v>93</v>
       </c>
       <c r="I485">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="J485">
         <v>0</v>
@@ -16062,19 +16062,19 @@
         <v>1</v>
       </c>
       <c r="E486" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="F486" t="s">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="G486" t="s">
         <v>25</v>
       </c>
       <c r="H486">
-        <v>95</v>
+        <v>67</v>
       </c>
       <c r="I486">
-        <v>102</v>
+        <v>78</v>
       </c>
       <c r="J486">
         <v>0</v>
@@ -16094,19 +16094,19 @@
         <v>1</v>
       </c>
       <c r="E487" t="s">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="F487" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="G487" t="s">
         <v>26</v>
       </c>
       <c r="H487">
-        <v>102</v>
+        <v>78</v>
       </c>
       <c r="I487">
-        <v>95</v>
+        <v>67</v>
       </c>
       <c r="J487">
         <v>0</v>
@@ -16126,19 +16126,19 @@
         <v>1</v>
       </c>
       <c r="E488" t="s">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="F488" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="G488" t="s">
         <v>25</v>
       </c>
       <c r="H488">
-        <v>69</v>
+        <v>95</v>
       </c>
       <c r="I488">
-        <v>83</v>
+        <v>102</v>
       </c>
       <c r="J488">
         <v>0</v>
@@ -16158,19 +16158,19 @@
         <v>1</v>
       </c>
       <c r="E489" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="F489" t="s">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="G489" t="s">
         <v>26</v>
       </c>
       <c r="H489">
-        <v>83</v>
+        <v>102</v>
       </c>
       <c r="I489">
-        <v>69</v>
+        <v>95</v>
       </c>
       <c r="J489">
         <v>0</v>
@@ -16178,7 +16178,7 @@
     </row>
     <row r="490" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A490" s="1">
-        <v>45559</v>
+        <v>45557</v>
       </c>
       <c r="B490">
         <v>2024</v>
@@ -16190,16 +16190,16 @@
         <v>1</v>
       </c>
       <c r="E490" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="F490" t="s">
-        <v>24</v>
+        <v>13</v>
       </c>
       <c r="G490" t="s">
         <v>25</v>
       </c>
       <c r="H490">
-        <v>76</v>
+        <v>69</v>
       </c>
       <c r="I490">
         <v>83</v>
@@ -16210,7 +16210,7 @@
     </row>
     <row r="491" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A491" s="1">
-        <v>45559</v>
+        <v>45557</v>
       </c>
       <c r="B491">
         <v>2024</v>
@@ -16222,10 +16222,10 @@
         <v>1</v>
       </c>
       <c r="E491" t="s">
-        <v>24</v>
+        <v>13</v>
       </c>
       <c r="F491" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="G491" t="s">
         <v>26</v>
@@ -16234,7 +16234,7 @@
         <v>83</v>
       </c>
       <c r="I491">
-        <v>76</v>
+        <v>69</v>
       </c>
       <c r="J491">
         <v>0</v>
@@ -16254,19 +16254,19 @@
         <v>1</v>
       </c>
       <c r="E492" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="F492" t="s">
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="G492" t="s">
         <v>25</v>
       </c>
       <c r="H492">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="I492">
-        <v>91</v>
+        <v>83</v>
       </c>
       <c r="J492">
         <v>0</v>
@@ -16286,19 +16286,19 @@
         <v>1</v>
       </c>
       <c r="E493" t="s">
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="F493" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="G493" t="s">
         <v>26</v>
       </c>
       <c r="H493">
-        <v>91</v>
+        <v>83</v>
       </c>
       <c r="I493">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="J493">
         <v>0</v>
@@ -16306,7 +16306,7 @@
     </row>
     <row r="494" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A494" s="1">
-        <v>45560</v>
+        <v>45559</v>
       </c>
       <c r="B494">
         <v>2024</v>
@@ -16318,19 +16318,19 @@
         <v>1</v>
       </c>
       <c r="E494" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="F494" t="s">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="G494" t="s">
         <v>25</v>
       </c>
       <c r="H494">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="I494">
-        <v>87</v>
+        <v>91</v>
       </c>
       <c r="J494">
         <v>0</v>
@@ -16338,7 +16338,7 @@
     </row>
     <row r="495" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A495" s="1">
-        <v>45560</v>
+        <v>45559</v>
       </c>
       <c r="B495">
         <v>2024</v>
@@ -16350,19 +16350,19 @@
         <v>1</v>
       </c>
       <c r="E495" t="s">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="F495" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="G495" t="s">
         <v>26</v>
       </c>
       <c r="H495">
-        <v>87</v>
+        <v>91</v>
       </c>
       <c r="I495">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="J495">
         <v>0</v>
@@ -16382,19 +16382,19 @@
         <v>1</v>
       </c>
       <c r="E496" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="F496" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="G496" t="s">
         <v>25</v>
       </c>
       <c r="H496">
-        <v>88</v>
+        <v>81</v>
       </c>
       <c r="I496">
-        <v>101</v>
+        <v>87</v>
       </c>
       <c r="J496">
         <v>0</v>
@@ -16414,19 +16414,19 @@
         <v>1</v>
       </c>
       <c r="E497" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="F497" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="G497" t="s">
         <v>26</v>
       </c>
       <c r="H497">
-        <v>101</v>
+        <v>87</v>
       </c>
       <c r="I497">
-        <v>88</v>
+        <v>81</v>
       </c>
       <c r="J497">
         <v>0</v>
@@ -16434,7 +16434,7 @@
     </row>
     <row r="498" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A498" s="1">
-        <v>45564</v>
+        <v>45560</v>
       </c>
       <c r="B498">
         <v>2024</v>
@@ -16443,10 +16443,10 @@
         <v>23</v>
       </c>
       <c r="D498">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E498" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="F498" t="s">
         <v>16</v>
@@ -16455,10 +16455,10 @@
         <v>25</v>
       </c>
       <c r="H498">
-        <v>73</v>
+        <v>88</v>
       </c>
       <c r="I498">
-        <v>70</v>
+        <v>101</v>
       </c>
       <c r="J498">
         <v>0</v>
@@ -16466,7 +16466,7 @@
     </row>
     <row r="499" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A499" s="1">
-        <v>45564</v>
+        <v>45560</v>
       </c>
       <c r="B499">
         <v>2024</v>
@@ -16475,22 +16475,22 @@
         <v>23</v>
       </c>
       <c r="D499">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E499" t="s">
         <v>16</v>
       </c>
       <c r="F499" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="G499" t="s">
         <v>26</v>
       </c>
       <c r="H499">
-        <v>70</v>
+        <v>101</v>
       </c>
       <c r="I499">
-        <v>73</v>
+        <v>88</v>
       </c>
       <c r="J499">
         <v>0</v>
@@ -16510,19 +16510,19 @@
         <v>2</v>
       </c>
       <c r="E500" t="s">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="F500" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="G500" t="s">
         <v>25</v>
       </c>
       <c r="H500">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="I500">
-        <v>87</v>
+        <v>70</v>
       </c>
       <c r="J500">
         <v>0</v>
@@ -16542,19 +16542,19 @@
         <v>2</v>
       </c>
       <c r="E501" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="F501" t="s">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="G501" t="s">
         <v>26</v>
       </c>
       <c r="H501">
-        <v>87</v>
+        <v>70</v>
       </c>
       <c r="I501">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="J501">
         <v>0</v>
@@ -16562,7 +16562,7 @@
     </row>
     <row r="502" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A502" s="1">
-        <v>45566</v>
+        <v>45564</v>
       </c>
       <c r="B502">
         <v>2024</v>
@@ -16574,19 +16574,19 @@
         <v>2</v>
       </c>
       <c r="E502" t="s">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="F502" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="G502" t="s">
         <v>25</v>
       </c>
       <c r="H502">
-        <v>70</v>
+        <v>77</v>
       </c>
       <c r="I502">
-        <v>77</v>
+        <v>87</v>
       </c>
       <c r="J502">
         <v>0</v>
@@ -16594,7 +16594,7 @@
     </row>
     <row r="503" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A503" s="1">
-        <v>45566</v>
+        <v>45564</v>
       </c>
       <c r="B503">
         <v>2024</v>
@@ -16606,19 +16606,19 @@
         <v>2</v>
       </c>
       <c r="E503" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="F503" t="s">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="G503" t="s">
         <v>26</v>
       </c>
       <c r="H503">
+        <v>87</v>
+      </c>
+      <c r="I503">
         <v>77</v>
-      </c>
-      <c r="I503">
-        <v>70</v>
       </c>
       <c r="J503">
         <v>0</v>
@@ -16638,19 +16638,19 @@
         <v>2</v>
       </c>
       <c r="E504" t="s">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="F504" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="G504" t="s">
         <v>25</v>
       </c>
       <c r="H504">
-        <v>84</v>
+        <v>70</v>
       </c>
       <c r="I504">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="J504">
         <v>0</v>
@@ -16670,19 +16670,19 @@
         <v>2</v>
       </c>
       <c r="E505" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="F505" t="s">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="G505" t="s">
         <v>26</v>
       </c>
       <c r="H505">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="I505">
-        <v>84</v>
+        <v>70</v>
       </c>
       <c r="J505">
         <v>0</v>
@@ -16690,7 +16690,7 @@
     </row>
     <row r="506" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A506" s="1">
-        <v>45569</v>
+        <v>45566</v>
       </c>
       <c r="B506">
         <v>2024</v>
@@ -16702,19 +16702,19 @@
         <v>2</v>
       </c>
       <c r="E506" t="s">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="F506" t="s">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="G506" t="s">
         <v>25</v>
       </c>
       <c r="H506">
-        <v>90</v>
+        <v>84</v>
       </c>
       <c r="I506">
-        <v>81</v>
+        <v>88</v>
       </c>
       <c r="J506">
         <v>0</v>
@@ -16722,7 +16722,7 @@
     </row>
     <row r="507" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A507" s="1">
-        <v>45569</v>
+        <v>45566</v>
       </c>
       <c r="B507">
         <v>2024</v>
@@ -16734,19 +16734,19 @@
         <v>2</v>
       </c>
       <c r="E507" t="s">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="F507" t="s">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="G507" t="s">
         <v>26</v>
       </c>
       <c r="H507">
-        <v>81</v>
+        <v>88</v>
       </c>
       <c r="I507">
-        <v>90</v>
+        <v>84</v>
       </c>
       <c r="J507">
         <v>0</v>
@@ -16766,19 +16766,19 @@
         <v>2</v>
       </c>
       <c r="E508" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="F508" t="s">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="G508" t="s">
         <v>25</v>
       </c>
       <c r="H508">
+        <v>90</v>
+      </c>
+      <c r="I508">
         <v>81</v>
-      </c>
-      <c r="I508">
-        <v>95</v>
       </c>
       <c r="J508">
         <v>0</v>
@@ -16798,19 +16798,19 @@
         <v>2</v>
       </c>
       <c r="E509" t="s">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="F509" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="G509" t="s">
         <v>26</v>
       </c>
       <c r="H509">
-        <v>95</v>
+        <v>81</v>
       </c>
       <c r="I509">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="J509">
         <v>0</v>
@@ -16818,7 +16818,7 @@
     </row>
     <row r="510" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A510" s="1">
-        <v>45571</v>
+        <v>45569</v>
       </c>
       <c r="B510">
         <v>2024</v>
@@ -16830,19 +16830,19 @@
         <v>2</v>
       </c>
       <c r="E510" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="F510" t="s">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="G510" t="s">
         <v>25</v>
       </c>
       <c r="H510">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="I510">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="J510">
         <v>0</v>
@@ -16850,7 +16850,7 @@
     </row>
     <row r="511" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A511" s="1">
-        <v>45571</v>
+        <v>45569</v>
       </c>
       <c r="B511">
         <v>2024</v>
@@ -16862,19 +16862,19 @@
         <v>2</v>
       </c>
       <c r="E511" t="s">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="F511" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="G511" t="s">
         <v>26</v>
       </c>
       <c r="H511">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="I511">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="J511">
         <v>0</v>
@@ -16894,19 +16894,19 @@
         <v>2</v>
       </c>
       <c r="E512" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="F512" t="s">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="G512" t="s">
         <v>25</v>
       </c>
       <c r="H512">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="I512">
-        <v>62</v>
+        <v>92</v>
       </c>
       <c r="J512">
         <v>0</v>
@@ -16926,19 +16926,19 @@
         <v>2</v>
       </c>
       <c r="E513" t="s">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="F513" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="G513" t="s">
         <v>26</v>
       </c>
       <c r="H513">
-        <v>62</v>
+        <v>92</v>
       </c>
       <c r="I513">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="J513">
         <v>0</v>
@@ -16946,7 +16946,7 @@
     </row>
     <row r="514" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A514" s="1">
-        <v>45573</v>
+        <v>45571</v>
       </c>
       <c r="B514">
         <v>2024</v>
@@ -16958,19 +16958,19 @@
         <v>2</v>
       </c>
       <c r="E514" t="s">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="F514" t="s">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="G514" t="s">
         <v>25</v>
       </c>
       <c r="H514">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="I514">
-        <v>88</v>
+        <v>62</v>
       </c>
       <c r="J514">
         <v>0</v>
@@ -16978,7 +16978,7 @@
     </row>
     <row r="515" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A515" s="1">
-        <v>45573</v>
+        <v>45571</v>
       </c>
       <c r="B515">
         <v>2024</v>
@@ -16990,19 +16990,19 @@
         <v>2</v>
       </c>
       <c r="E515" t="s">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="F515" t="s">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="G515" t="s">
         <v>26</v>
       </c>
       <c r="H515">
-        <v>88</v>
+        <v>62</v>
       </c>
       <c r="I515">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="J515">
         <v>0</v>
@@ -17010,7 +17010,7 @@
     </row>
     <row r="516" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A516" s="1">
-        <v>45575</v>
+        <v>45573</v>
       </c>
       <c r="B516">
         <v>2024</v>
@@ -17019,30 +17019,30 @@
         <v>23</v>
       </c>
       <c r="D516">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E516" t="s">
+        <v>19</v>
+      </c>
+      <c r="F516" t="s">
         <v>16</v>
       </c>
-      <c r="F516" t="s">
-        <v>13</v>
-      </c>
       <c r="G516" t="s">
         <v>25</v>
       </c>
       <c r="H516">
-        <v>95</v>
+        <v>77</v>
       </c>
       <c r="I516">
-        <v>93</v>
+        <v>88</v>
       </c>
       <c r="J516">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="517" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A517" s="1">
-        <v>45575</v>
+        <v>45573</v>
       </c>
       <c r="B517">
         <v>2024</v>
@@ -17051,30 +17051,30 @@
         <v>23</v>
       </c>
       <c r="D517">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E517" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="F517" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="G517" t="s">
         <v>26</v>
       </c>
       <c r="H517">
-        <v>93</v>
+        <v>88</v>
       </c>
       <c r="I517">
-        <v>95</v>
+        <v>77</v>
       </c>
       <c r="J517">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="518" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A518" s="1">
-        <v>45578</v>
+        <v>45575</v>
       </c>
       <c r="B518">
         <v>2024</v>
@@ -17095,18 +17095,18 @@
         <v>25</v>
       </c>
       <c r="H518">
-        <v>66</v>
+        <v>95</v>
       </c>
       <c r="I518">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="J518">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="519" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A519" s="1">
-        <v>45578</v>
+        <v>45575</v>
       </c>
       <c r="B519">
         <v>2024</v>
@@ -17127,18 +17127,18 @@
         <v>26</v>
       </c>
       <c r="H519">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="I519">
-        <v>66</v>
+        <v>95</v>
       </c>
       <c r="J519">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="520" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A520" s="1">
-        <v>45581</v>
+        <v>45578</v>
       </c>
       <c r="B520">
         <v>2024</v>
@@ -17150,19 +17150,19 @@
         <v>3</v>
       </c>
       <c r="E520" t="s">
+        <v>16</v>
+      </c>
+      <c r="F520" t="s">
         <v>13</v>
       </c>
-      <c r="F520" t="s">
-        <v>16</v>
-      </c>
       <c r="G520" t="s">
         <v>25</v>
       </c>
       <c r="H520">
+        <v>66</v>
+      </c>
+      <c r="I520">
         <v>80</v>
-      </c>
-      <c r="I520">
-        <v>77</v>
       </c>
       <c r="J520">
         <v>0</v>
@@ -17170,7 +17170,7 @@
     </row>
     <row r="521" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A521" s="1">
-        <v>45581</v>
+        <v>45578</v>
       </c>
       <c r="B521">
         <v>2024</v>
@@ -17182,19 +17182,19 @@
         <v>3</v>
       </c>
       <c r="E521" t="s">
+        <v>13</v>
+      </c>
+      <c r="F521" t="s">
         <v>16</v>
       </c>
-      <c r="F521" t="s">
-        <v>13</v>
-      </c>
       <c r="G521" t="s">
         <v>26</v>
       </c>
       <c r="H521">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="I521">
-        <v>80</v>
+        <v>66</v>
       </c>
       <c r="J521">
         <v>0</v>
@@ -17202,7 +17202,7 @@
     </row>
     <row r="522" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A522" s="1">
-        <v>45583</v>
+        <v>45581</v>
       </c>
       <c r="B522">
         <v>2024</v>
@@ -17226,7 +17226,7 @@
         <v>80</v>
       </c>
       <c r="I522">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="J522">
         <v>0</v>
@@ -17234,7 +17234,7 @@
     </row>
     <row r="523" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A523" s="1">
-        <v>45583</v>
+        <v>45581</v>
       </c>
       <c r="B523">
         <v>2024</v>
@@ -17255,7 +17255,7 @@
         <v>26</v>
       </c>
       <c r="H523">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="I523">
         <v>80</v>
@@ -17266,7 +17266,7 @@
     </row>
     <row r="524" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A524" s="1">
-        <v>45585</v>
+        <v>45583</v>
       </c>
       <c r="B524">
         <v>2024</v>
@@ -17278,27 +17278,27 @@
         <v>3</v>
       </c>
       <c r="E524" t="s">
+        <v>13</v>
+      </c>
+      <c r="F524" t="s">
         <v>16</v>
       </c>
-      <c r="F524" t="s">
-        <v>13</v>
-      </c>
       <c r="G524" t="s">
         <v>25</v>
       </c>
       <c r="H524">
-        <v>62</v>
+        <v>80</v>
       </c>
       <c r="I524">
-        <v>67</v>
+        <v>82</v>
       </c>
       <c r="J524">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="525" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A525" s="1">
-        <v>45585</v>
+        <v>45583</v>
       </c>
       <c r="B525">
         <v>2024</v>
@@ -17310,21 +17310,85 @@
         <v>3</v>
       </c>
       <c r="E525" t="s">
+        <v>16</v>
+      </c>
+      <c r="F525" t="s">
         <v>13</v>
       </c>
-      <c r="F525" t="s">
+      <c r="G525" t="s">
+        <v>26</v>
+      </c>
+      <c r="H525">
+        <v>82</v>
+      </c>
+      <c r="I525">
+        <v>80</v>
+      </c>
+      <c r="J525">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="526" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A526" s="1">
+        <v>45585</v>
+      </c>
+      <c r="B526">
+        <v>2024</v>
+      </c>
+      <c r="C526" t="s">
+        <v>23</v>
+      </c>
+      <c r="D526">
+        <v>3</v>
+      </c>
+      <c r="E526" t="s">
         <v>16</v>
       </c>
-      <c r="G525" t="s">
-        <v>26</v>
-      </c>
-      <c r="H525">
+      <c r="F526" t="s">
+        <v>13</v>
+      </c>
+      <c r="G526" t="s">
+        <v>25</v>
+      </c>
+      <c r="H526">
+        <v>62</v>
+      </c>
+      <c r="I526">
         <v>67</v>
       </c>
-      <c r="I525">
+      <c r="J526">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="527" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A527" s="1">
+        <v>45585</v>
+      </c>
+      <c r="B527">
+        <v>2024</v>
+      </c>
+      <c r="C527" t="s">
+        <v>23</v>
+      </c>
+      <c r="D527">
+        <v>3</v>
+      </c>
+      <c r="E527" t="s">
+        <v>13</v>
+      </c>
+      <c r="F527" t="s">
+        <v>16</v>
+      </c>
+      <c r="G527" t="s">
+        <v>26</v>
+      </c>
+      <c r="H527">
+        <v>67</v>
+      </c>
+      <c r="I527">
         <v>62</v>
       </c>
-      <c r="J525">
+      <c r="J527">
         <v>1</v>
       </c>
     </row>
